--- a/dataset/ficheros/clientes.xlsx
+++ b/dataset/ficheros/clientes.xlsx
@@ -519,7 +519,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -544,7 +544,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>info@cafeteriaelmolino.es</t>
+          <t>cafeteriaelmolino1@gmail.com</t>
         </is>
       </c>
       <c r="I2" s="2" t="n">
@@ -563,11 +563,7 @@
       <c r="L2" t="n">
         <v>3</v>
       </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Abre solo fines de semana en invierno</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -582,7 +578,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -628,7 +624,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Paga a 30 días</t>
+          <t>Cerrado los lunes</t>
         </is>
       </c>
     </row>
@@ -645,7 +641,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HOSTELERIA</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -670,7 +666,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>info@mesonmanolo.es</t>
+          <t>mesonmanolo3@hotmail.com</t>
         </is>
       </c>
       <c r="I4" s="2" t="n">
@@ -689,11 +685,7 @@
       <c r="L4" t="n">
         <v>5</v>
       </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Cambió de dueño en 2023</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -733,7 +725,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>isabelcobo4@telefonica.net</t>
+          <t>isabelcobo4@outlook.es</t>
         </is>
       </c>
       <c r="I5" s="2" t="n">
@@ -752,7 +744,11 @@
       <c r="L5" t="n">
         <v>0</v>
       </c>
-      <c r="M5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>Entrar por la parte de atrás</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -811,11 +807,7 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>Descarga complicada, calle estrecha</t>
-        </is>
-      </c>
+      <c r="M6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -870,7 +862,11 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="M7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>Preguntar por Charo</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -883,11 +879,7 @@
           <t>José Cobo</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Particular</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>C/ Ruamayor 32</t>
@@ -929,11 +921,7 @@
       <c r="L8" t="n">
         <v>0</v>
       </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Ojo con la factura</t>
-        </is>
-      </c>
+      <c r="M8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -946,11 +934,7 @@
           <t>Isabel Mazo</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Particular</t>
-        </is>
-      </c>
+      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>C/ Mayor 33</t>
@@ -961,10 +945,8 @@
           <t>Laredo</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>39770</t>
-        </is>
+      <c r="F9" t="n">
+        <v>39770</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -973,7 +955,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>isabelmazo8@outlook.es</t>
+          <t>isabelmazo8@yahoo.es</t>
         </is>
       </c>
       <c r="I9" s="2" t="n">
@@ -1007,7 +989,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>hosteleria</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1051,11 +1033,7 @@
       <c r="L10" t="n">
         <v>10</v>
       </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>No hay nadie por la tarde</t>
-        </is>
-      </c>
+      <c r="M10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1083,17 +1061,19 @@
           <t>Reinosa</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>39200</t>
-        </is>
+      <c r="F11" t="n">
+        <v>39200</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
           <t>942345485</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>elenaibanez10@outlook.es</t>
+        </is>
+      </c>
       <c r="I11" s="2" t="n">
         <v>44556</v>
       </c>
@@ -1112,7 +1092,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Cerrado en febrero</t>
+          <t>Cambió de dueño en 2023</t>
         </is>
       </c>
     </row>
@@ -1129,7 +1109,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>hosteleria</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1173,11 +1153,7 @@
       <c r="L12" t="n">
         <v>8</v>
       </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Cliente antiguo</t>
-        </is>
-      </c>
+      <c r="M12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1217,7 +1193,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>carmengutierrez12@outlook.es</t>
+          <t>carmengutierrez12@movistar.es</t>
         </is>
       </c>
       <c r="I13" s="2" t="n">
@@ -1276,7 +1252,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>martavillegas13@yahoo.es</t>
+          <t>martavillegas13@outlook.es</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
@@ -1310,7 +1286,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1335,7 +1311,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>rubenherrera14@outlook.es</t>
+          <t>rubenherrera14@gmail.com</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
@@ -1354,7 +1330,11 @@
       <c r="L15" t="n">
         <v>0</v>
       </c>
-      <c r="M15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>Ojo con la factura</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1394,7 +1374,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>fernandomazo15@outlook.es</t>
+          <t>fernandomazo15@telefonica.net</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
@@ -1428,7 +1408,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1453,7 +1433,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>pizzerialaermita16@gmail.com</t>
+          <t>info@pizzerialaermita.es</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
@@ -1512,7 +1492,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>javierobregon17@hotmail.com</t>
+          <t>javierobregon17@yahoo.es</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
@@ -1531,7 +1511,11 @@
       <c r="L18" t="n">
         <v>0</v>
       </c>
-      <c r="M18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>Preguntar por Charo</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1546,7 +1530,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>hosteleria</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1569,7 +1553,11 @@
           <t>634 89 48 54</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>mesoncasaelena18@gmail.com</t>
+        </is>
+      </c>
       <c r="I19" s="2" t="n">
         <v>44260</v>
       </c>
@@ -1601,7 +1589,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HOSTELERIA</t>
+          <t>hosteleria</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1626,7 +1614,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>pensioncasaelena19@movistar.es</t>
+          <t>pensioncasaelena19@hotmail.com</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
@@ -1685,7 +1673,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>elenabustamante20@yahoo.es</t>
+          <t>elenabustamante20.yahoo.es</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
@@ -1719,7 +1707,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1742,11 +1730,7 @@
           <t>985106394</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>pedrobolado21@yahoo.es</t>
-        </is>
-      </c>
+      <c r="H22" t="inlineStr"/>
       <c r="I22" s="2" t="n">
         <v>43609</v>
       </c>
@@ -1765,7 +1749,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Cambió de dueño en 2023</t>
+          <t>Paga a 30 días</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1766,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1807,7 +1791,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>javiernoriega22@telefonica.net</t>
+          <t>javiernoriega22@outlook.es</t>
         </is>
       </c>
       <c r="I23" s="2" t="n">
@@ -1845,7 +1829,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1870,7 +1854,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>franciscoherrera23@movistar.es</t>
+          <t>franciscoherrera23@gmail.com</t>
         </is>
       </c>
       <c r="I24" s="2" t="n">
@@ -1929,7 +1913,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>javiercorral24@hotmail.com</t>
+          <t>javiercorral24@gmail.com</t>
         </is>
       </c>
       <c r="I25" s="2" t="n">
@@ -1963,7 +1947,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>hosteleria</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2009,7 +1993,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>No hay nadie por la tarde</t>
+          <t>Cerrado los lunes</t>
         </is>
       </c>
     </row>
@@ -2026,7 +2010,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2110,7 +2094,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>elenagutierrez27@gmail.com</t>
+          <t>elenagutierrez27@movistar.es</t>
         </is>
       </c>
       <c r="I28" s="2" t="n">
@@ -2192,12 +2176,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mesón Los Arcos</t>
+          <t>MesÃ³n Los Arcos</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2222,7 +2206,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>mesonlosarcos29@gmail.com</t>
+          <t>info@mesonlosarcos.es</t>
         </is>
       </c>
       <c r="I30" s="2" t="n">
@@ -2279,11 +2263,7 @@
           <t>+34942754911</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>pensionlaermita30@telefonica.net</t>
-        </is>
-      </c>
+      <c r="H31" t="inlineStr"/>
       <c r="I31" s="2" t="n">
         <v>44141</v>
       </c>
@@ -2374,7 +2354,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -2397,11 +2377,7 @@
           <t>+34942604375</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>laurapuente32@yahoo.es</t>
-        </is>
-      </c>
+      <c r="H33" t="inlineStr"/>
       <c r="I33" s="2" t="n">
         <v>43890</v>
       </c>
@@ -2418,11 +2394,7 @@
       <c r="L33" t="n">
         <v>3</v>
       </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Solo garrafas</t>
-        </is>
-      </c>
+      <c r="M33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -2462,7 +2434,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>lauracorral33@hotmail.com</t>
+          <t>lauracorral33@outlook.es</t>
         </is>
       </c>
       <c r="I34" s="2" t="n">
@@ -2501,7 +2473,7 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>C/ Santa Lucía 22</t>
+          <t>C/ Santa LucÃ­a 22</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -2519,11 +2491,19 @@
           <t>942-70-27-27</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>lauraquintana34@hotmail.com</t>
+        </is>
+      </c>
       <c r="I35" s="2" t="n">
         <v>45044</v>
       </c>
-      <c r="J35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>RUTA-1</t>
+        </is>
+      </c>
       <c r="K35" t="inlineStr">
         <is>
           <t>domiciliado</t>
@@ -2572,7 +2552,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>beatrizposada35@yahoo.es</t>
+          <t>beatrizposada35@movistar.es</t>
         </is>
       </c>
       <c r="I36" s="2" t="n">
@@ -2591,7 +2571,11 @@
       <c r="L36" t="n">
         <v>3</v>
       </c>
-      <c r="M36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>El reparto pasa sobre las 7 y media</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -2631,7 +2615,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>antoniovillar36@hotmail.com</t>
+          <t>antoniovillar36@outlook.es</t>
         </is>
       </c>
       <c r="I37" s="2" t="n">
@@ -2709,7 +2693,11 @@
       <c r="L38" t="n">
         <v>0</v>
       </c>
-      <c r="M38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Descarga complicada, calle estrecha</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -2724,7 +2712,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2749,7 +2737,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>sergiodiego38@yahoo.es</t>
+          <t>sergiodiego38@outlook.es</t>
         </is>
       </c>
       <c r="I39" s="2" t="n">
@@ -2783,7 +2771,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2806,11 +2794,7 @@
           <t>942289336</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>tabernacasaelena39@outlook.es</t>
-        </is>
-      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" s="2" t="n">
         <v>44773</v>
       </c>
@@ -2842,7 +2826,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2867,7 +2851,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>info@tabernaelbosque.es</t>
+          <t>tabernaelbosque40@telefonica.net</t>
         </is>
       </c>
       <c r="I41" s="2" t="n">
@@ -2888,7 +2872,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Preguntar por Charo</t>
+          <t>Abre solo fines de semana en invierno</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2889,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2930,7 +2914,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>antonioquintana41@movistar.es</t>
+          <t>antonioquintana41@outlook.es</t>
         </is>
       </c>
       <c r="I42" s="2" t="n">
@@ -2949,11 +2933,7 @@
       <c r="L42" t="n">
         <v>0</v>
       </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Entrar por la parte de atrás</t>
-        </is>
-      </c>
+      <c r="M42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -2968,7 +2948,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HOSTELERIA</t>
+          <t>hosteleria</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2993,7 +2973,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>info@cafeteriaelcantabr.es</t>
+          <t>cafeteriaelcantabrico42@movistar.es</t>
         </is>
       </c>
       <c r="I43" s="2" t="n">
@@ -3014,7 +2994,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Entrar por la parte de atrás</t>
+          <t>Cambió de dueño en 2023</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3034,11 @@
           <t>942-94-87-39</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>pizzeriaeltonel43@hotmail.com</t>
+        </is>
+      </c>
       <c r="I44" s="2" t="n">
         <v>43353</v>
       </c>
@@ -3071,11 +3055,7 @@
       <c r="L44" t="n">
         <v>3</v>
       </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Cerrado en febrero</t>
-        </is>
-      </c>
+      <c r="M44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -3088,7 +3068,11 @@
           <t>Lucía Pérez</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr"/>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Particular</t>
+        </is>
+      </c>
       <c r="D45" t="inlineStr">
         <is>
           <t>Barrio Somahoz 21</t>
@@ -3111,7 +3095,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>luciaperez44@hotmail.com</t>
+          <t>luciaperez44@yahoo.es</t>
         </is>
       </c>
       <c r="I45" s="2" t="n">
@@ -3130,11 +3114,7 @@
       <c r="L45" t="n">
         <v>0</v>
       </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Solo garrafas</t>
-        </is>
-      </c>
+      <c r="M45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -3174,7 +3154,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>albertopalacio45@yahoo.es</t>
+          <t>albertopalacio45@gmail.com</t>
         </is>
       </c>
       <c r="I46" s="2" t="n">
@@ -3203,12 +3183,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Pizzería Casa Julián</t>
+          <t>PizzerÃ­a Casa JuliÃ¡n</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>HOSTELERIA</t>
+          <t>hosteleria</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -3233,7 +3213,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>pizzeriacasajulian46@outlook.es</t>
+          <t>pizzeriacasajulian46@hotmail.com</t>
         </is>
       </c>
       <c r="I47" s="2" t="n">
@@ -3267,7 +3247,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -3370,11 +3350,7 @@
       <c r="L49" t="n">
         <v>0</v>
       </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>Preguntar por Charo</t>
-        </is>
-      </c>
+      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3402,8 +3378,10 @@
           <t>Los Corrales de Buelna</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>39400</v>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>39400</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -3412,7 +3390,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>pilaribanez49@telefonica.net</t>
+          <t>pilaribanez49@hotmail.com</t>
         </is>
       </c>
       <c r="I50" s="2" t="n">
@@ -3428,9 +3406,7 @@
           <t>domiciliado</t>
         </is>
       </c>
-      <c r="L50" t="n">
-        <v>0</v>
-      </c>
+      <c r="L50" t="inlineStr"/>
       <c r="M50" t="inlineStr"/>
     </row>
     <row r="51">
@@ -3446,7 +3422,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -3471,7 +3447,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>anavillar50@telefonica.net</t>
+          <t>anavillar50.hotmail.com</t>
         </is>
       </c>
       <c r="I51" s="2" t="n">
@@ -3490,11 +3466,7 @@
       <c r="L51" t="n">
         <v>0</v>
       </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>Abre solo fines de semana en invierno</t>
-        </is>
-      </c>
+      <c r="M51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -3509,7 +3481,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -3534,7 +3506,7 @@
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>restaurantecasajulian51@hotmail.com</t>
+          <t>info@restaurantecasajul.es</t>
         </is>
       </c>
       <c r="I52" s="2" t="n">
@@ -3563,12 +3535,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Mesón La Bodega</t>
+          <t>MesÃ³n La Bodega</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>hosteleria</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -3581,21 +3553,27 @@
           <t>El Astillero</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>39610</t>
-        </is>
+      <c r="F53" t="n">
+        <v>39610</v>
       </c>
       <c r="G53" t="inlineStr">
         <is>
           <t>942 31 37 70</t>
         </is>
       </c>
-      <c r="H53" t="inlineStr"/>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>mesonlabodega52@hotmail.com</t>
+        </is>
+      </c>
       <c r="I53" s="2" t="n">
         <v>44348</v>
       </c>
-      <c r="J53" t="inlineStr"/>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>RUTA-1</t>
+        </is>
+      </c>
       <c r="K53" t="inlineStr">
         <is>
           <t>transferencia</t>
@@ -3619,7 +3597,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -3642,11 +3620,7 @@
           <t>942 74 27 35</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>carmensaiz53@outlook.es</t>
-        </is>
-      </c>
+      <c r="H54" t="inlineStr"/>
       <c r="I54" s="2" t="n">
         <v>42981</v>
       </c>
@@ -3703,7 +3677,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>carmenibanez54@telefonica.net</t>
+          <t>carmenibanez54@hotmail.com</t>
         </is>
       </c>
       <c r="I55" s="2" t="n">
@@ -3722,7 +3696,11 @@
       <c r="L55" t="n">
         <v>0</v>
       </c>
-      <c r="M55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>Llamar antes de ir</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3760,11 +3738,7 @@
           <t>985 54 55 85</t>
         </is>
       </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>javiermazo55@telefonica.net</t>
-        </is>
-      </c>
+      <c r="H56" t="inlineStr"/>
       <c r="I56" s="2" t="n">
         <v>44964</v>
       </c>
@@ -3821,13 +3795,17 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>info@cafecasapepe.es</t>
+          <t>cafecasapepe56@yahoo.es</t>
         </is>
       </c>
       <c r="I57" s="2" t="n">
         <v>43666</v>
       </c>
-      <c r="J57" t="inlineStr"/>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>RUTA-3</t>
+        </is>
+      </c>
       <c r="K57" t="inlineStr">
         <is>
           <t>efectivo</t>
@@ -3895,7 +3873,11 @@
       <c r="L58" t="n">
         <v>0</v>
       </c>
-      <c r="M58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>El reparto pasa sobre las 7 y media</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3910,7 +3892,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -3935,7 +3917,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>patriciaescalante58@telefonica.net</t>
+          <t>patriciaescalante58@outlook.es</t>
         </is>
       </c>
       <c r="I59" s="2" t="n">
@@ -3954,11 +3936,7 @@
       <c r="L59" t="n">
         <v>0</v>
       </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Preguntar por Charo</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3973,7 +3951,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -3998,7 +3976,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>ivanortiz59.gmail.com</t>
+          <t>ivanortiz59@gmail.com</t>
         </is>
       </c>
       <c r="I60" s="2" t="n">
@@ -4032,7 +4010,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>HOSTELERIA</t>
+          <t>hosteleria</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -4057,7 +4035,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>cerveceriacasajulian60@hotmail.com</t>
+          <t>cerveceriacasajulian60@outlook.es</t>
         </is>
       </c>
       <c r="I61" s="2" t="n">
@@ -4076,11 +4054,7 @@
       <c r="L61" t="n">
         <v>5</v>
       </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>Entrar por la parte de atrás</t>
-        </is>
-      </c>
+      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -4095,7 +4069,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -4118,7 +4092,11 @@
           <t>722-19-70-02</t>
         </is>
       </c>
-      <c r="H62" t="inlineStr"/>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>fernandocuadrado61@outlook.es</t>
+        </is>
+      </c>
       <c r="I62" s="2" t="n">
         <v>44630</v>
       </c>
@@ -4175,7 +4153,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>info@asadorcasaelena.es</t>
+          <t>asadorcasaelena62@movistar.es</t>
         </is>
       </c>
       <c r="I63" s="2" t="n">
@@ -4194,11 +4172,7 @@
       <c r="L63" t="n">
         <v>3</v>
       </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>Cambió de dueño en 2023</t>
-        </is>
-      </c>
+      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -4208,12 +4182,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MarisquerÃ­a El Bosque</t>
+          <t>Marisquería El Bosque</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -4236,11 +4210,7 @@
           <t>985 90 00 38</t>
         </is>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>marisqueriaelbosque63@hotmail.com</t>
-        </is>
-      </c>
+      <c r="H64" t="inlineStr"/>
       <c r="I64" s="2" t="n">
         <v>44828</v>
       </c>
@@ -4254,7 +4224,9 @@
           <t>efectivo</t>
         </is>
       </c>
-      <c r="L64" t="inlineStr"/>
+      <c r="L64" t="n">
+        <v>0</v>
+      </c>
       <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
@@ -4270,7 +4242,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -4293,7 +4265,11 @@
           <t>942 86 29 05</t>
         </is>
       </c>
-      <c r="H65" t="inlineStr"/>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>raulruiz64@outlook.es</t>
+        </is>
+      </c>
       <c r="I65" s="2" t="n">
         <v>45163</v>
       </c>
@@ -4310,11 +4286,7 @@
       <c r="L65" t="n">
         <v>0</v>
       </c>
-      <c r="M65" t="inlineStr">
-        <is>
-          <t>Preguntar por Charo</t>
-        </is>
-      </c>
+      <c r="M65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -4352,11 +4324,7 @@
           <t>942219198</t>
         </is>
       </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>luciasolana65@gmail.com</t>
-        </is>
-      </c>
+      <c r="H66" t="inlineStr"/>
       <c r="I66" s="2" t="n">
         <v>45093</v>
       </c>
@@ -4373,7 +4341,11 @@
       <c r="L66" t="n">
         <v>0</v>
       </c>
-      <c r="M66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>Cerrado los lunes</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -4388,7 +4360,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -4413,7 +4385,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>barrestaurantecasajuli66@hotmail.com</t>
+          <t>barrestaurantecasajuli66@outlook.es</t>
         </is>
       </c>
       <c r="I67" s="2" t="n">
@@ -4434,7 +4406,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Preguntar por Charo</t>
+          <t>Descarga complicada, calle estrecha</t>
         </is>
       </c>
     </row>
@@ -4446,7 +4418,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>PizzerÃ­a El Sardinero</t>
+          <t>Pizzería El Sardinero</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -4476,7 +4448,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>pizzeriaelsardinero67@telefonica.net</t>
+          <t>info@pizzeriaelsardiner.es</t>
         </is>
       </c>
       <c r="I68" s="2" t="n">
@@ -4510,7 +4482,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>HOSTELERIA</t>
+          <t>hosteleria</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -4535,7 +4507,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>barlaescalinata68@gmail.com</t>
+          <t>info@barlaescalinata.es</t>
         </is>
       </c>
       <c r="I69" s="2" t="n">
@@ -4554,11 +4526,7 @@
       <c r="L69" t="n">
         <v>10</v>
       </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>Ojo con la factura</t>
-        </is>
-      </c>
+      <c r="M69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4568,7 +4536,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Óscar Trueba</t>
+          <t>Ãscar Trueba</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -4598,7 +4566,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>oscartrueba69@yahoo.es</t>
+          <t>oscartrueba69@hotmail.com</t>
         </is>
       </c>
       <c r="I70" s="2" t="n">
@@ -4617,7 +4585,11 @@
       <c r="L70" t="n">
         <v>0</v>
       </c>
-      <c r="M70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>Tiene fuente en alquiler</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4655,25 +4627,19 @@
           <t>658-02-30-08</t>
         </is>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>rosaposada70.hotmail.com</t>
-        </is>
-      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" s="2" t="n">
         <v>44869</v>
       </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>RUTA-3</t>
-        </is>
-      </c>
+      <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr">
         <is>
           <t>transferencia</t>
         </is>
       </c>
-      <c r="L71" t="inlineStr"/>
+      <c r="L71" t="n">
+        <v>0</v>
+      </c>
       <c r="M71" t="inlineStr"/>
     </row>
     <row r="72">
@@ -4689,7 +4655,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -4712,11 +4678,7 @@
           <t>+34617563291</t>
         </is>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>rubencorral71@telefonica.net</t>
-        </is>
-      </c>
+      <c r="H72" t="inlineStr"/>
       <c r="I72" s="2" t="n">
         <v>43633</v>
       </c>
@@ -4735,7 +4697,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Abre solo fines de semana en invierno</t>
+          <t>Entrar por la parte de atrás</t>
         </is>
       </c>
     </row>
@@ -4747,7 +4709,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Lucía Gutiérrez</t>
+          <t>LucÃ­a GutiÃ©rrez</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -4775,11 +4737,19 @@
           <t>631369243</t>
         </is>
       </c>
-      <c r="H73" t="inlineStr"/>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>luciagutierrez72@hotmail.com</t>
+        </is>
+      </c>
       <c r="I73" s="2" t="n">
         <v>44097</v>
       </c>
-      <c r="J73" t="inlineStr"/>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>RUTA-4</t>
+        </is>
+      </c>
       <c r="K73" t="inlineStr">
         <is>
           <t>domiciliado</t>
@@ -4788,7 +4758,11 @@
       <c r="L73" t="n">
         <v>0</v>
       </c>
-      <c r="M73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>Ojo con la factura</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -4828,7 +4802,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>carmencorral73@movistar.es</t>
+          <t>carmencorral73@yahoo.es</t>
         </is>
       </c>
       <c r="I74" s="2" t="n">
@@ -4847,11 +4821,7 @@
       <c r="L74" t="n">
         <v>0</v>
       </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>No hay nadie por la tarde</t>
-        </is>
-      </c>
+      <c r="M74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -4866,12 +4836,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>C/ del Río 79</t>
+          <t>C/ del RÃ­o 79</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -4912,7 +4882,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>No hay nadie por la tarde</t>
+          <t>Ojo con la factura</t>
         </is>
       </c>
     </row>
@@ -4929,7 +4899,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>hosteleria</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -4954,7 +4924,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>sidrerialaherradura75@yahoo.es</t>
+          <t>sidrerialaherradura75@movistar.es</t>
         </is>
       </c>
       <c r="I76" s="2" t="n">
@@ -4975,7 +4945,7 @@
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>Abre solo fines de semana en invierno</t>
+          <t>Entrar por la parte de atrás</t>
         </is>
       </c>
     </row>
@@ -4992,7 +4962,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -5070,7 +5040,11 @@
           <t>942-42-74-33</t>
         </is>
       </c>
-      <c r="H78" t="inlineStr"/>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>carlospuente77@outlook.es</t>
+        </is>
+      </c>
       <c r="I78" s="2" t="n">
         <v>42166</v>
       </c>
@@ -5087,7 +5061,11 @@
       <c r="L78" t="n">
         <v>0</v>
       </c>
-      <c r="M78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>Cerrado en febrero</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -5097,17 +5075,17 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Marisquería Casa Julián</t>
+          <t>MarisquerÃ­a Casa JuliÃ¡n</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>C/ Menéndez Pelayo 74</t>
+          <t>C/ MenÃ©ndez Pelayo 74</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -5127,7 +5105,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>marisqueriacasajulian78@gmail.com</t>
+          <t>info@marisqueriacasajul.es</t>
         </is>
       </c>
       <c r="I79" s="2" t="n">
@@ -5146,11 +5124,7 @@
       <c r="L79" t="n">
         <v>8</v>
       </c>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>Cerrado en febrero</t>
-        </is>
-      </c>
+      <c r="M79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -5188,7 +5162,11 @@
           <t>985-37-10-82</t>
         </is>
       </c>
-      <c r="H80" t="inlineStr"/>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>manuelceballos79.movistar.es</t>
+        </is>
+      </c>
       <c r="I80" s="2" t="n">
         <v>42626</v>
       </c>
@@ -5205,7 +5183,11 @@
       <c r="L80" t="n">
         <v>0</v>
       </c>
-      <c r="M80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Ojo con la factura</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -5245,7 +5227,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>pedrorivas80@movistar.es</t>
+          <t>pedrorivas80@hotmail.com</t>
         </is>
       </c>
       <c r="I81" s="2" t="n">
@@ -5264,7 +5246,11 @@
       <c r="L81" t="n">
         <v>0</v>
       </c>
-      <c r="M81" t="inlineStr"/>
+      <c r="M81" t="inlineStr">
+        <is>
+          <t>Ojo con la factura</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -5302,7 +5288,11 @@
           <t>651 05 38 73</t>
         </is>
       </c>
-      <c r="H82" t="inlineStr"/>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>barrestaurantelaherrad81@movistar.es</t>
+        </is>
+      </c>
       <c r="I82" s="2" t="n">
         <v>45450</v>
       </c>
@@ -5329,7 +5319,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Lucía Cobo</t>
+          <t>LucÃ­a Cobo</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -5357,11 +5347,7 @@
           <t>942774554</t>
         </is>
       </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>luciacobo82@yahoo.es</t>
-        </is>
-      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" s="2" t="n">
         <v>42833</v>
       </c>
@@ -5378,11 +5364,7 @@
       <c r="L83" t="n">
         <v>0</v>
       </c>
-      <c r="M83" t="inlineStr">
-        <is>
-          <t>Ojo con la factura</t>
-        </is>
-      </c>
+      <c r="M83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -5397,7 +5379,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -5422,7 +5404,7 @@
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>ivancorral83@movistar.es</t>
+          <t>ivancorral83@hotmail.com</t>
         </is>
       </c>
       <c r="I84" s="2" t="n">
@@ -5479,11 +5461,7 @@
           <t>+34942474534</t>
         </is>
       </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>info@barlaplaza.es</t>
-        </is>
-      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" s="2" t="n">
         <v>44734</v>
       </c>
@@ -5515,7 +5493,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -5555,11 +5533,7 @@
       <c r="L86" t="n">
         <v>0</v>
       </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>Tiene fuente en alquiler</t>
-        </is>
-      </c>
+      <c r="M86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -5599,7 +5573,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>nuriaruiz86@outlook.es</t>
+          <t>nuriaruiz86@yahoo.es</t>
         </is>
       </c>
       <c r="I87" s="2" t="n">
@@ -5615,12 +5589,10 @@
           <t>transferencia</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>Entrar por la parte de atrás</t>
-        </is>
-      </c>
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -5635,7 +5607,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -5658,11 +5630,7 @@
           <t>+34942736114</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>pedroquintana87@hotmail.com</t>
-        </is>
-      </c>
+      <c r="H88" t="inlineStr"/>
       <c r="I88" s="2" t="n">
         <v>43502</v>
       </c>
@@ -5694,12 +5662,12 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>C/ Santa LucÃ­a 47</t>
+          <t>C/ Santa Lucía 47</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -5719,7 +5687,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>isabelsolana88@gmail.com</t>
+          <t>isabelsolana88@outlook.es</t>
         </is>
       </c>
       <c r="I89" s="2" t="n">
@@ -5753,7 +5721,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -5778,7 +5746,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>restauranteelsardinero89.yahoo.es</t>
+          <t>info@restauranteelsardi.es</t>
         </is>
       </c>
       <c r="I90" s="2" t="n">
@@ -5837,7 +5805,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>ivanherrera90@outlook.es</t>
+          <t>ivanherrera90@yahoo.es</t>
         </is>
       </c>
       <c r="I91" s="2" t="n">
@@ -5871,7 +5839,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -5894,11 +5862,7 @@
           <t>942-03-78-28</t>
         </is>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>carmencobo91@movistar.es</t>
-        </is>
-      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" s="2" t="n">
         <v>44346</v>
       </c>
@@ -5989,7 +5953,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -6046,7 +6010,11 @@
           <t>Pilar Corral</t>
         </is>
       </c>
-      <c r="C95" t="inlineStr"/>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>part.</t>
+        </is>
+      </c>
       <c r="D95" t="inlineStr">
         <is>
           <t>C/ Alta 13</t>
@@ -6069,7 +6037,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>pilarcorral94@gmail.com</t>
+          <t>pilarcorral94@movistar.es</t>
         </is>
       </c>
       <c r="I95" s="2" t="n">
@@ -6103,7 +6071,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -6126,11 +6094,7 @@
           <t>681332477</t>
         </is>
       </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>antoniogomez95@movistar.es</t>
-        </is>
-      </c>
+      <c r="H96" t="inlineStr"/>
       <c r="I96" s="2" t="n">
         <v>45400</v>
       </c>
@@ -6147,7 +6111,11 @@
       <c r="L96" t="n">
         <v>0</v>
       </c>
-      <c r="M96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>Abre solo fines de semana en invierno</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -6162,7 +6130,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -6185,7 +6153,11 @@
           <t>985 18 16 86</t>
         </is>
       </c>
-      <c r="H97" t="inlineStr"/>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>antoniobolado96@yahoo.es</t>
+        </is>
+      </c>
       <c r="I97" s="2" t="n">
         <v>44931</v>
       </c>
@@ -6202,11 +6174,7 @@
       <c r="L97" t="n">
         <v>0</v>
       </c>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>Paga a 30 días</t>
-        </is>
-      </c>
+      <c r="M97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -6221,7 +6189,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -6246,7 +6214,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>angelquintana97@outlook.es</t>
+          <t>angelquintana97@hotmail.com</t>
         </is>
       </c>
       <c r="I98" s="2" t="n">
@@ -6265,7 +6233,11 @@
       <c r="L98" t="n">
         <v>0</v>
       </c>
-      <c r="M98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>Paga a 30 días</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -6280,7 +6252,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -6324,11 +6296,7 @@
       <c r="L99" t="n">
         <v>0</v>
       </c>
-      <c r="M99" t="inlineStr">
-        <is>
-          <t>Pide albarán siempre</t>
-        </is>
-      </c>
+      <c r="M99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -6343,7 +6311,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -6368,7 +6336,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>marisquerialaria99@outlook.es</t>
+          <t>info@marisquerialaria.es</t>
         </is>
       </c>
       <c r="I100" s="2" t="n">
@@ -6402,7 +6370,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>HOSTELERIA</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -6427,7 +6395,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>hotellaterraza100@gmail.com</t>
+          <t>hotellaterraza100@yahoo.es</t>
         </is>
       </c>
       <c r="I101" s="2" t="n">
@@ -6456,7 +6424,7 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Pizzería La Terraza</t>
+          <t>PizzerÃ­a La Terraza</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
@@ -6486,7 +6454,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>info@pizzerialaterraza.es</t>
+          <t>pizzerialaterraza101@hotmail.com</t>
         </is>
       </c>
       <c r="I102" s="2" t="n">
@@ -6505,11 +6473,7 @@
       <c r="L102" t="n">
         <v>12</v>
       </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>Cambió de dueño en 2023</t>
-        </is>
-      </c>
+      <c r="M102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -6524,7 +6488,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -6549,7 +6513,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>luisherrera102@yahoo.es</t>
+          <t>luisherrera102@hotmail.com</t>
         </is>
       </c>
       <c r="I103" s="2" t="n">
@@ -6570,7 +6534,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Entrar por la parte de atrás</t>
+          <t>Llamar antes de ir</t>
         </is>
       </c>
     </row>
@@ -6585,11 +6549,7 @@
           <t>Juan Quintana</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>Particular</t>
-        </is>
-      </c>
+      <c r="C104" t="inlineStr"/>
       <c r="D104" t="inlineStr">
         <is>
           <t>C/ Isabel II 32</t>
@@ -6610,15 +6570,15 @@
           <t>942052097</t>
         </is>
       </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>juanquintana103@telefonica.net</t>
-        </is>
-      </c>
+      <c r="H104" t="inlineStr"/>
       <c r="I104" s="2" t="n">
         <v>45211</v>
       </c>
-      <c r="J104" t="inlineStr"/>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>RUTA-2</t>
+        </is>
+      </c>
       <c r="K104" t="inlineStr">
         <is>
           <t>domiciliado</t>
@@ -6642,12 +6602,12 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>C/ Peña Herbosa 55</t>
+          <t>C/ PeÃ±a Herbosa 55</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -6665,7 +6625,11 @@
           <t>620826024</t>
         </is>
       </c>
-      <c r="H105" t="inlineStr"/>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>mesonelbosque104@movistar.es</t>
+        </is>
+      </c>
       <c r="I105" s="2" t="n">
         <v>45086</v>
       </c>
@@ -6682,7 +6646,11 @@
       <c r="L105" t="n">
         <v>5</v>
       </c>
-      <c r="M105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>Ojo con la factura</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -6710,10 +6678,8 @@
           <t>Los Corrales de Buelna</t>
         </is>
       </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>39400</t>
-        </is>
+      <c r="F106" t="n">
+        <v>39400</v>
       </c>
       <c r="G106" t="inlineStr">
         <is>
@@ -6722,7 +6688,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>barelcruce105@gmail.com</t>
+          <t>barelcruce105@movistar.es</t>
         </is>
       </c>
       <c r="I106" s="2" t="n">
@@ -6756,7 +6722,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>HOSTELERIA</t>
+          <t>hosteleria</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -6779,11 +6745,7 @@
           <t>985089133</t>
         </is>
       </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>info@sidrerialaria.es</t>
-        </is>
-      </c>
+      <c r="H107" t="inlineStr"/>
       <c r="I107" s="2" t="n">
         <v>44751</v>
       </c>
@@ -6800,11 +6762,7 @@
       <c r="L107" t="n">
         <v>0</v>
       </c>
-      <c r="M107" t="inlineStr">
-        <is>
-          <t>Abre solo fines de semana en invierno</t>
-        </is>
-      </c>
+      <c r="M107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -6824,7 +6782,7 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>C/ Santa LucÃ­a 20</t>
+          <t>C/ Santa Lucía 20</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -6844,7 +6802,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>analavin107@outlook.es</t>
+          <t>analavin107@movistar.es</t>
         </is>
       </c>
       <c r="I108" s="2" t="n">
@@ -6865,7 +6823,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Cliente antiguo</t>
+          <t>Entrar por la parte de atrás</t>
         </is>
       </c>
     </row>
@@ -6882,7 +6840,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -6907,7 +6865,7 @@
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>manuelsalces108.yahoo.es</t>
+          <t>manuelsalces108@movistar.es</t>
         </is>
       </c>
       <c r="I109" s="2" t="n">
@@ -6926,11 +6884,7 @@
       <c r="L109" t="n">
         <v>0</v>
       </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>Entrar por la parte de atrás</t>
-        </is>
-      </c>
+      <c r="M109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -6968,7 +6922,11 @@
           <t>647 40 87 31</t>
         </is>
       </c>
-      <c r="H110" t="inlineStr"/>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>rubenibanez109@hotmail.com</t>
+        </is>
+      </c>
       <c r="I110" s="2" t="n">
         <v>43779</v>
       </c>
@@ -6985,7 +6943,11 @@
       <c r="L110" t="n">
         <v>0</v>
       </c>
-      <c r="M110" t="inlineStr"/>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>Cambió de dueño en 2023</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -7000,7 +6962,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -7023,15 +6985,15 @@
           <t>682-36-31-46</t>
         </is>
       </c>
-      <c r="H111" t="inlineStr"/>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>info@tabernaelmolino.es</t>
+        </is>
+      </c>
       <c r="I111" s="2" t="n">
         <v>44993</v>
       </c>
-      <c r="J111" t="inlineStr">
-        <is>
-          <t>RUTA-2</t>
-        </is>
-      </c>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
           <t>domiciliado</t>
@@ -7050,12 +7012,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Café El Cantón</t>
+          <t>CafÃ© El CantÃ³n</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -7078,7 +7040,11 @@
           <t>677 32 04 54</t>
         </is>
       </c>
-      <c r="H112" t="inlineStr"/>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>cafeelcanton111@hotmail.com</t>
+        </is>
+      </c>
       <c r="I112" s="2" t="n">
         <v>43997</v>
       </c>
@@ -7105,17 +7071,17 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Óscar Mazo</t>
+          <t>Ãscar Mazo</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>C/ Menéndez Pelayo 23</t>
+          <t>C/ MenÃ©ndez Pelayo 23</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -7135,7 +7101,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>oscarmazo112.hotmail.com</t>
+          <t>oscarmazo112@gmail.com</t>
         </is>
       </c>
       <c r="I113" s="2" t="n">
@@ -7154,11 +7120,7 @@
       <c r="L113" t="n">
         <v>0</v>
       </c>
-      <c r="M113" t="inlineStr">
-        <is>
-          <t>Entrar por la parte de atrás</t>
-        </is>
-      </c>
+      <c r="M113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -7173,7 +7135,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>HOSTELERIA</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -7198,7 +7160,7 @@
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>info@asadormanolo.es</t>
+          <t>asadormanolo113@yahoo.es</t>
         </is>
       </c>
       <c r="I114" s="2" t="n">
@@ -7217,11 +7179,7 @@
       <c r="L114" t="n">
         <v>10</v>
       </c>
-      <c r="M114" t="inlineStr">
-        <is>
-          <t>Entrar por la parte de atrás</t>
-        </is>
-      </c>
+      <c r="M114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -7236,7 +7194,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -7261,7 +7219,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>franciscomazo114@yahoo.es</t>
+          <t>franciscomazo114@telefonica.net</t>
         </is>
       </c>
       <c r="I115" s="2" t="n">
@@ -7282,7 +7240,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Entrar por la parte de atrás</t>
+          <t>No hay nadie antes de las 9</t>
         </is>
       </c>
     </row>
@@ -7324,7 +7282,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>isabelibanez115@gmail.com</t>
+          <t>isabelibanez115@yahoo.es</t>
         </is>
       </c>
       <c r="I116" s="2" t="n">
@@ -7358,7 +7316,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>HOSTELERIA</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -7371,10 +7329,8 @@
           <t>Llanes</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>33500</t>
-        </is>
+      <c r="F117" t="n">
+        <v>33500</v>
       </c>
       <c r="G117" t="inlineStr">
         <is>
@@ -7383,7 +7339,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>info.barrestauranteelmo.es</t>
+          <t>info@barrestauranteelmo.es</t>
         </is>
       </c>
       <c r="I117" s="2" t="n">
@@ -7402,11 +7358,7 @@
       <c r="L117" t="n">
         <v>10</v>
       </c>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>Cliente antiguo</t>
-        </is>
-      </c>
+      <c r="M117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -7461,7 +7413,11 @@
       <c r="L118" t="n">
         <v>3</v>
       </c>
-      <c r="M118" t="inlineStr"/>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>Descarga complicada, calle estrecha</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -7476,7 +7432,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -7501,7 +7457,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>info@hotellaria.es</t>
+          <t>hotellaria118@telefonica.net</t>
         </is>
       </c>
       <c r="I119" s="2" t="n">
@@ -7535,7 +7491,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -7577,7 +7533,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Preguntar por Charo</t>
+          <t>Cerrado en febrero</t>
         </is>
       </c>
     </row>
@@ -7589,7 +7545,7 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Pensión Casa Pepe</t>
+          <t>PensiÃ³n Casa Pepe</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -7617,7 +7573,11 @@
           <t>637 66 45 33</t>
         </is>
       </c>
-      <c r="H121" t="inlineStr"/>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>pensioncasapepe120@outlook.es</t>
+        </is>
+      </c>
       <c r="I121" s="2" t="n">
         <v>43148</v>
       </c>
@@ -7649,7 +7609,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -7662,8 +7622,10 @@
           <t>Santander</t>
         </is>
       </c>
-      <c r="F122" t="n">
-        <v>39008</v>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>39008</t>
+        </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
@@ -7672,7 +7634,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>anacorral121@telefonica.net</t>
+          <t>anacorral121@gmail.com</t>
         </is>
       </c>
       <c r="I122" s="2" t="n">
@@ -7706,7 +7668,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -7729,7 +7691,11 @@
           <t>642 72 56 93</t>
         </is>
       </c>
-      <c r="H123" t="inlineStr"/>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>sergioruiz122@gmail.com</t>
+        </is>
+      </c>
       <c r="I123" s="2" t="n">
         <v>43582</v>
       </c>
@@ -7746,11 +7712,7 @@
       <c r="L123" t="n">
         <v>0</v>
       </c>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>Cerrado los lunes</t>
-        </is>
-      </c>
+      <c r="M123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -7778,8 +7740,10 @@
           <t>Los Corrales de Buelna</t>
         </is>
       </c>
-      <c r="F124" t="n">
-        <v>39400</v>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>39400</t>
+        </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
@@ -7788,7 +7752,7 @@
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>mariavillegas123@hotmail.com</t>
+          <t>mariavillegas123@yahoo.es</t>
         </is>
       </c>
       <c r="I124" s="2" t="n">
@@ -7822,7 +7786,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -7847,7 +7811,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>pedrocuadrado124@gmail.com</t>
+          <t>pedrocuadrado124@hotmail.com</t>
         </is>
       </c>
       <c r="I125" s="2" t="n">
@@ -7866,7 +7830,11 @@
       <c r="L125" t="n">
         <v>0</v>
       </c>
-      <c r="M125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>Preguntar por Charo</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -7940,7 +7908,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -7963,7 +7931,11 @@
           <t>+34942393245</t>
         </is>
       </c>
-      <c r="H127" t="inlineStr"/>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>sarafernandez126@movistar.es</t>
+        </is>
+      </c>
       <c r="I127" s="2" t="n">
         <v>43768</v>
       </c>
@@ -7980,11 +7952,7 @@
       <c r="L127" t="n">
         <v>0</v>
       </c>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>Tiene fuente en alquiler</t>
-        </is>
-      </c>
+      <c r="M127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -8024,7 +7992,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>hotelelpuerto127@hotmail.com</t>
+          <t>hotelelpuerto127@movistar.es</t>
         </is>
       </c>
       <c r="I128" s="2" t="n">
@@ -8058,7 +8026,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -8102,11 +8070,7 @@
       <c r="L129" t="n">
         <v>0</v>
       </c>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>Ojo con la factura</t>
-        </is>
-      </c>
+      <c r="M129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -8121,7 +8085,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -8146,7 +8110,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>info@hotelelnogal.es</t>
+          <t>hotelelnogal129@outlook.es</t>
         </is>
       </c>
       <c r="I130" s="2" t="n">
@@ -8165,11 +8129,7 @@
       <c r="L130" t="n">
         <v>3</v>
       </c>
-      <c r="M130" t="inlineStr">
-        <is>
-          <t>Llamar antes de ir</t>
-        </is>
-      </c>
+      <c r="M130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -8184,7 +8144,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -8209,7 +8169,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>oscarposada130@gmail.com</t>
+          <t>oscarposada130@outlook.es</t>
         </is>
       </c>
       <c r="I131" s="2" t="n">
@@ -8268,7 +8228,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>antoniomazo131@gmail.com</t>
+          <t>antoniomazo131@yahoo.es</t>
         </is>
       </c>
       <c r="I132" s="2" t="n">
@@ -8302,7 +8262,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -8327,7 +8287,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>carlossaiz132@hotmail.com</t>
+          <t>carlossaiz132@movistar.es</t>
         </is>
       </c>
       <c r="I133" s="2" t="n">
@@ -8346,11 +8306,7 @@
       <c r="L133" t="n">
         <v>0</v>
       </c>
-      <c r="M133" t="inlineStr">
-        <is>
-          <t>Descarga complicada, calle estrecha</t>
-        </is>
-      </c>
+      <c r="M133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -8363,7 +8319,11 @@
           <t>Antonio Gutiérrez</t>
         </is>
       </c>
-      <c r="C134" t="inlineStr"/>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Particular</t>
+        </is>
+      </c>
       <c r="D134" t="inlineStr">
         <is>
           <t>Barrio La Iglesia 40</t>
@@ -8420,7 +8380,7 @@
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -8445,7 +8405,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>miguelposada134@gmail.com</t>
+          <t>miguelposada134@outlook.es</t>
         </is>
       </c>
       <c r="I135" s="2" t="n">
@@ -8466,7 +8426,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Descarga complicada, calle estrecha</t>
+          <t>No hay nadie antes de las 9</t>
         </is>
       </c>
     </row>
@@ -8506,7 +8466,11 @@
           <t>+34942425406</t>
         </is>
       </c>
-      <c r="H136" t="inlineStr"/>
+      <c r="H136" t="inlineStr">
+        <is>
+          <t>marisqueriaelpescador135@movistar.es</t>
+        </is>
+      </c>
       <c r="I136" s="2" t="n">
         <v>44423</v>
       </c>
@@ -8536,7 +8500,11 @@
           <t>Elena Corral</t>
         </is>
       </c>
-      <c r="C137" t="inlineStr"/>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Particular</t>
+        </is>
+      </c>
       <c r="D137" t="inlineStr">
         <is>
           <t>Barrio El Cruce 81</t>
@@ -8547,10 +8515,8 @@
           <t>San Vicente de la Barquera</t>
         </is>
       </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>39540</t>
-        </is>
+      <c r="F137" t="n">
+        <v>39540</v>
       </c>
       <c r="G137" t="inlineStr">
         <is>
@@ -8559,7 +8525,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>elenacorral136@telefonica.net</t>
+          <t>elenacorral136@yahoo.es</t>
         </is>
       </c>
       <c r="I137" s="2" t="n">
@@ -8578,7 +8544,11 @@
       <c r="L137" t="n">
         <v>0</v>
       </c>
-      <c r="M137" t="inlineStr"/>
+      <c r="M137" t="inlineStr">
+        <is>
+          <t>No hay nadie por la tarde</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -8593,7 +8563,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -8616,7 +8586,11 @@
           <t>+34942374626</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr"/>
+      <c r="H138" t="inlineStr">
+        <is>
+          <t>info@cafelaria.es</t>
+        </is>
+      </c>
       <c r="I138" s="2" t="n">
         <v>42153</v>
       </c>
@@ -8673,7 +8647,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>mesoncasapepe138@gmail.com</t>
+          <t>info@mesoncasapepe.es</t>
         </is>
       </c>
       <c r="I139" s="2" t="n">
@@ -8707,7 +8681,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -8720,8 +8694,10 @@
           <t>Ribadesella</t>
         </is>
       </c>
-      <c r="F140" t="n">
-        <v>33560</v>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>33560</t>
+        </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
@@ -8730,7 +8706,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>info@chiringuitolaherra.es</t>
+          <t>chiringuitolaherradura139@gmail.com</t>
         </is>
       </c>
       <c r="I140" s="2" t="n">
@@ -8751,7 +8727,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Pide albarán siempre</t>
+          <t>Paga a 30 días</t>
         </is>
       </c>
     </row>
@@ -8773,7 +8749,7 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Avda. de España 62</t>
+          <t>Avda. de EspaÃ±a 62</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -8791,11 +8767,7 @@
           <t>+34698303822</t>
         </is>
       </c>
-      <c r="H141" t="inlineStr">
-        <is>
-          <t>ivanperez140@gmail.com</t>
-        </is>
-      </c>
+      <c r="H141" t="inlineStr"/>
       <c r="I141" s="2" t="n">
         <v>45236</v>
       </c>
@@ -8858,7 +8830,11 @@
       <c r="I142" s="2" t="n">
         <v>43584</v>
       </c>
-      <c r="J142" t="inlineStr"/>
+      <c r="J142" t="inlineStr">
+        <is>
+          <t>RUTA-4</t>
+        </is>
+      </c>
       <c r="K142" t="inlineStr">
         <is>
           <t>domiciliado</t>
@@ -8867,11 +8843,7 @@
       <c r="L142" t="n">
         <v>5</v>
       </c>
-      <c r="M142" t="inlineStr">
-        <is>
-          <t>Entrar por la parte de atrás</t>
-        </is>
-      </c>
+      <c r="M142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -8911,7 +8883,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>pizzeriacasanieves142@movistar.es</t>
+          <t>pizzeriacasanieves142.gmail.com</t>
         </is>
       </c>
       <c r="I143" s="2" t="n">
@@ -8930,11 +8902,7 @@
       <c r="L143" t="n">
         <v>0</v>
       </c>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>Solo garrafas</t>
-        </is>
-      </c>
+      <c r="M143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -8954,7 +8922,7 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>C/ General DÃ¡vila 55</t>
+          <t>C/ General Dávila 55</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -9033,24 +9001,26 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>mariabustamante144@gmail.com</t>
+          <t>mariabustamante144@yahoo.es</t>
         </is>
       </c>
       <c r="I145" s="2" t="n">
         <v>42977</v>
       </c>
-      <c r="J145" t="inlineStr">
-        <is>
-          <t>RUTA-2</t>
-        </is>
-      </c>
+      <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
           <t>domiciliado</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr"/>
-      <c r="M145" t="inlineStr"/>
+      <c r="L145" t="n">
+        <v>0</v>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>Llamar antes de ir</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -9060,7 +9030,7 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Ángel Ruiz</t>
+          <t>Ãngel Ruiz</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
@@ -9124,7 +9094,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -9149,7 +9119,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>chiringuitoelcantabric146@movistar.es</t>
+          <t>chiringuitoelcantabric146@hotmail.com</t>
         </is>
       </c>
       <c r="I147" s="2" t="n">
@@ -9188,7 +9158,7 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>C/ Santa Lucía 65</t>
+          <t>C/ Santa LucÃ­a 65</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -9225,7 +9195,7 @@
       </c>
       <c r="M148" t="inlineStr">
         <is>
-          <t>Paga a 30 días</t>
+          <t>Ojo con la factura</t>
         </is>
       </c>
     </row>
@@ -9237,12 +9207,12 @@
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Sidrería Los Pinos</t>
+          <t>SidrerÃ­a Los Pinos</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>hosteleria</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -9265,11 +9235,7 @@
           <t>650 81 29 02</t>
         </is>
       </c>
-      <c r="H149" t="inlineStr">
-        <is>
-          <t>sidrerialospinos148@telefonica.net</t>
-        </is>
-      </c>
+      <c r="H149" t="inlineStr"/>
       <c r="I149" s="2" t="n">
         <v>43278</v>
       </c>
@@ -9286,7 +9252,11 @@
       <c r="L149" t="n">
         <v>3</v>
       </c>
-      <c r="M149" t="inlineStr"/>
+      <c r="M149" t="inlineStr">
+        <is>
+          <t>Cambió de dueño en 2023</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -9326,7 +9296,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>jesuscorral149@yahoo.es</t>
+          <t>jesuscorral149@gmail.com</t>
         </is>
       </c>
       <c r="I150" s="2" t="n">
@@ -9345,11 +9315,7 @@
       <c r="L150" t="n">
         <v>0</v>
       </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>Paga a 30 días</t>
-        </is>
-      </c>
+      <c r="M150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -9364,7 +9330,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>HOSTELERIA</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -9387,11 +9353,7 @@
           <t>942-48-54-24</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
-        <is>
-          <t>restaurantelacuadra150@yahoo.es</t>
-        </is>
-      </c>
+      <c r="H151" t="inlineStr"/>
       <c r="I151" s="2" t="n">
         <v>43166</v>
       </c>
@@ -9410,7 +9372,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Solo garrafas</t>
+          <t>Cerrado los lunes</t>
         </is>
       </c>
     </row>
@@ -9427,7 +9389,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -9471,7 +9433,11 @@
       <c r="L152" t="n">
         <v>10</v>
       </c>
-      <c r="M152" t="inlineStr"/>
+      <c r="M152" t="inlineStr">
+        <is>
+          <t>Descarga complicada, calle estrecha</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -9484,11 +9450,7 @@
           <t>Laura Gutiérrez</t>
         </is>
       </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Particular</t>
-        </is>
-      </c>
+      <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr">
         <is>
           <t>Barrio El Cruce 14</t>
@@ -9509,7 +9471,11 @@
           <t>942 99 20 89</t>
         </is>
       </c>
-      <c r="H153" t="inlineStr"/>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>lauragutierrez152@yahoo.es</t>
+        </is>
+      </c>
       <c r="I153" s="2" t="n">
         <v>42552</v>
       </c>
@@ -9528,7 +9494,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Ojo con la factura</t>
+          <t>Entrar por la parte de atrás</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9509,11 @@
           <t>Antonio Higuera</t>
         </is>
       </c>
-      <c r="C154" t="inlineStr"/>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>part.</t>
+        </is>
+      </c>
       <c r="D154" t="inlineStr">
         <is>
           <t>C/ Isabel II 30</t>
@@ -9564,11 +9534,7 @@
           <t>+34942854613</t>
         </is>
       </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>antoniohiguera153@movistar.es</t>
-        </is>
-      </c>
+      <c r="H154" t="inlineStr"/>
       <c r="I154" s="2" t="n">
         <v>44590</v>
       </c>
@@ -9646,7 +9612,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>Solo garrafas</t>
+          <t>Tiene fuente en alquiler</t>
         </is>
       </c>
     </row>
@@ -9658,12 +9624,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>ANTONIO VILLAR</t>
+          <t>Villar, Antonio</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -9676,10 +9642,8 @@
           <t>Torrelavega</t>
         </is>
       </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>39300</t>
-        </is>
+      <c r="F156" t="n">
+        <v>39300</v>
       </c>
       <c r="G156" t="inlineStr">
         <is>
@@ -9688,7 +9652,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>antoniovillar155@hotmail.com</t>
+          <t>villarantonio155@movistar.es</t>
         </is>
       </c>
       <c r="I156" s="2" t="n">
@@ -9707,7 +9671,11 @@
       <c r="L156" t="n">
         <v>0</v>
       </c>
-      <c r="M156" t="inlineStr"/>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>Solo garrafas</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -9745,11 +9713,7 @@
           <t>942 51 14 01</t>
         </is>
       </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>info@sidrerialaermita.es</t>
-        </is>
-      </c>
+      <c r="H157" t="inlineStr"/>
       <c r="I157" s="2" t="n">
         <v>42755</v>
       </c>
@@ -9781,12 +9745,12 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>C/ Peña Herbosa 67</t>
+          <t>C/ PeÃ±a Herbosa 67</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -9841,7 +9805,7 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>C/ Peña Herbosa 15</t>
+          <t>C/ PeÃ±a Herbosa 15</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -9861,7 +9825,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>barcasaaurora158@outlook.es</t>
+          <t>barcasaaurora158.telefonica.net</t>
         </is>
       </c>
       <c r="I159" s="2" t="n">
@@ -9880,11 +9844,7 @@
       <c r="L159" t="n">
         <v>0</v>
       </c>
-      <c r="M159" t="inlineStr">
-        <is>
-          <t>Descarga complicada, calle estrecha</t>
-        </is>
-      </c>
+      <c r="M159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -9943,7 +9903,11 @@
       <c r="L160" t="n">
         <v>0</v>
       </c>
-      <c r="M160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>Ojo con la factura</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -9958,12 +9922,12 @@
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Avda. de España 73</t>
+          <t>Avda. de EspaÃ±a 73</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -9981,11 +9945,7 @@
           <t>+34666830320</t>
         </is>
       </c>
-      <c r="H161" t="inlineStr">
-        <is>
-          <t>miguelherrera160@telefonica.net</t>
-        </is>
-      </c>
+      <c r="H161" t="inlineStr"/>
       <c r="I161" s="2" t="n">
         <v>44202</v>
       </c>
@@ -10004,7 +9964,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Abre solo fines de semana en invierno</t>
+          <t>El reparto pasa sobre las 7 y media</t>
         </is>
       </c>
     </row>
@@ -10021,7 +9981,7 @@
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -10046,7 +10006,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>jesusruiz161@outlook.es</t>
+          <t>jesusruiz161@gmail.com</t>
         </is>
       </c>
       <c r="I162" s="2" t="n">
@@ -10080,7 +10040,7 @@
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>HOSTELERIA</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -10105,7 +10065,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>cafelaperla162@yahoo.es</t>
+          <t>cafelaperla162@hotmail.com</t>
         </is>
       </c>
       <c r="I163" s="2" t="n">
@@ -10164,7 +10124,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>pilarcuadrado163@gmail.com</t>
+          <t>pilarcuadrado163@hotmail.com</t>
         </is>
       </c>
       <c r="I164" s="2" t="n">
@@ -10183,7 +10143,11 @@
       <c r="L164" t="n">
         <v>0</v>
       </c>
-      <c r="M164" t="inlineStr"/>
+      <c r="M164" t="inlineStr">
+        <is>
+          <t>Pide albarán siempre</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -10198,12 +10162,12 @@
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>TravesÃ­a del Muelle 52</t>
+          <t>Travesía del Muelle 52</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -10242,7 +10206,11 @@
       <c r="L165" t="n">
         <v>0</v>
       </c>
-      <c r="M165" t="inlineStr"/>
+      <c r="M165" t="inlineStr">
+        <is>
+          <t>Cambió de dueño en 2023</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -10255,11 +10223,7 @@
           <t>Lucía Fernández</t>
         </is>
       </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Particular</t>
-        </is>
-      </c>
+      <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr">
         <is>
           <t>C/ Santa Lucía 58</t>
@@ -10282,7 +10246,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>luciafernandez165@gmail.com</t>
+          <t>luciafernandez165@yahoo.es</t>
         </is>
       </c>
       <c r="I166" s="2" t="n">
@@ -10301,11 +10265,7 @@
       <c r="L166" t="n">
         <v>0</v>
       </c>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>Paga a 30 días</t>
-        </is>
-      </c>
+      <c r="M166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -10345,7 +10305,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>info@mesoncasatino.es</t>
+          <t>mesoncasatino166@movistar.es</t>
         </is>
       </c>
       <c r="I167" s="2" t="n">
@@ -10364,7 +10324,11 @@
       <c r="L167" t="n">
         <v>8</v>
       </c>
-      <c r="M167" t="inlineStr"/>
+      <c r="M167" t="inlineStr">
+        <is>
+          <t>Pide albarán siempre</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -10404,7 +10368,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>jesussaiz167@gmail.com</t>
+          <t>jesussaiz167@yahoo.es</t>
         </is>
       </c>
       <c r="I168" s="2" t="n">
@@ -10438,7 +10402,7 @@
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -10463,7 +10427,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>raulcobo168@yahoo.es</t>
+          <t>raulcobo168@gmail.com</t>
         </is>
       </c>
       <c r="I169" s="2" t="n">
@@ -10479,10 +10443,12 @@
           <t>transferencia</t>
         </is>
       </c>
-      <c r="L169" t="n">
-        <v>0</v>
-      </c>
-      <c r="M169" t="inlineStr"/>
+      <c r="L169" t="inlineStr"/>
+      <c r="M169" t="inlineStr">
+        <is>
+          <t>Ojo con la factura</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -10492,12 +10458,12 @@
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>FRANCISCO HERRERA</t>
+          <t>F. Herrera</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -10520,7 +10486,11 @@
           <t>942-16-84-04</t>
         </is>
       </c>
-      <c r="H170" t="inlineStr"/>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>fherrera169@outlook.es</t>
+        </is>
+      </c>
       <c r="I170" s="2" t="n">
         <v>43042</v>
       </c>
@@ -10552,7 +10522,7 @@
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -10577,7 +10547,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>mariarivas170@movistar.es</t>
+          <t>mariarivas170@gmail.com</t>
         </is>
       </c>
       <c r="I171" s="2" t="n">
@@ -10606,12 +10576,12 @@
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>PensiÃ³n La Terraza</t>
+          <t>Pensión La Terraza</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -10651,11 +10621,7 @@
       <c r="L172" t="n">
         <v>5</v>
       </c>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>Preguntar por Charo</t>
-        </is>
-      </c>
+      <c r="M172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -10670,7 +10636,7 @@
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -10695,7 +10661,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>martavillar172@hotmail.com</t>
+          <t>martavillar172@gmail.com</t>
         </is>
       </c>
       <c r="I173" s="2" t="n">
@@ -10714,7 +10680,11 @@
       <c r="L173" t="n">
         <v>0</v>
       </c>
-      <c r="M173" t="inlineStr"/>
+      <c r="M173" t="inlineStr">
+        <is>
+          <t>Paga a 30 días</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -10729,7 +10699,7 @@
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -10769,7 +10739,11 @@
       <c r="L174" t="n">
         <v>0</v>
       </c>
-      <c r="M174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>Cerrado los lunes</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -10809,7 +10783,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>hotelelmuelle174@hotmail.com</t>
+          <t>hotelelmuelle174@outlook.es</t>
         </is>
       </c>
       <c r="I175" s="2" t="n">
@@ -10828,7 +10802,11 @@
       <c r="L175" t="n">
         <v>10</v>
       </c>
-      <c r="M175" t="inlineStr"/>
+      <c r="M175" t="inlineStr">
+        <is>
+          <t>Solo garrafas</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -10841,14 +10819,10 @@
           <t>Pensión El Pescador</t>
         </is>
       </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>Hostelería</t>
-        </is>
-      </c>
+      <c r="C176" t="inlineStr"/>
       <c r="D176" t="inlineStr">
         <is>
-          <t>C/ Peña Herbosa 72</t>
+          <t>C/ PeÃ±a Herbosa 72</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -10868,7 +10842,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>info@pensionelpescador.es</t>
+          <t>pensionelpescador175@telefonica.net</t>
         </is>
       </c>
       <c r="I176" s="2" t="n">
@@ -10887,11 +10861,7 @@
       <c r="L176" t="n">
         <v>10</v>
       </c>
-      <c r="M176" t="inlineStr">
-        <is>
-          <t>Llamar antes de ir</t>
-        </is>
-      </c>
+      <c r="M176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -10911,7 +10881,7 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Pº de Pereda 1</t>
+          <t>PÂº de Pereda 1</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -10931,7 +10901,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>pilarlavin176@outlook.es</t>
+          <t>pilarlavin176@hotmail.com</t>
         </is>
       </c>
       <c r="I177" s="2" t="n">
@@ -10990,7 +10960,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>pilarceballos177@gmail.com</t>
+          <t>pilarceballos177@telefonica.net</t>
         </is>
       </c>
       <c r="I178" s="2" t="n">
@@ -11006,9 +10976,7 @@
           <t>transferencia</t>
         </is>
       </c>
-      <c r="L178" t="n">
-        <v>0</v>
-      </c>
+      <c r="L178" t="inlineStr"/>
       <c r="M178" t="inlineStr"/>
     </row>
     <row r="179">
@@ -11019,12 +10987,12 @@
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>LAURA CORRAL S.L.</t>
+          <t>LAURA CORRAL</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -11049,7 +11017,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>lauracorralsl178@movistar.es</t>
+          <t>lauracorral178@gmail.com</t>
         </is>
       </c>
       <c r="I179" s="2" t="n">
@@ -11066,9 +11034,13 @@
         </is>
       </c>
       <c r="L179" t="n">
-        <v>12</v>
-      </c>
-      <c r="M179" t="inlineStr"/>
+        <v>3</v>
+      </c>
+      <c r="M179" t="inlineStr">
+        <is>
+          <t>Ojo con la factura</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -11083,12 +11055,12 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Avda. de España 27</t>
+          <t>Avda. de EspaÃ±a 27</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -11106,11 +11078,7 @@
           <t>652266580</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
-        <is>
-          <t>isabelherrera179@telefonica.net</t>
-        </is>
-      </c>
+      <c r="H180" t="inlineStr"/>
       <c r="I180" s="2" t="n">
         <v>43682</v>
       </c>
@@ -11127,7 +11095,11 @@
       <c r="L180" t="n">
         <v>0</v>
       </c>
-      <c r="M180" t="inlineStr"/>
+      <c r="M180" t="inlineStr">
+        <is>
+          <t>Cerrado los lunes</t>
+        </is>
+      </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -11137,12 +11109,12 @@
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Sidrería El Muelle</t>
+          <t>SidrerÃ­a El Muelle</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -11167,7 +11139,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>sidreriaelmuelle180@outlook.es</t>
+          <t>sidreriaelmuelle180@yahoo.es</t>
         </is>
       </c>
       <c r="I181" s="2" t="n">
@@ -11201,7 +11173,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -11226,7 +11198,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>albertoquintana181@yahoo.es</t>
+          <t>albertoquintana181@gmail.com</t>
         </is>
       </c>
       <c r="I182" s="2" t="n">
@@ -11245,7 +11217,11 @@
       <c r="L182" t="n">
         <v>0</v>
       </c>
-      <c r="M182" t="inlineStr"/>
+      <c r="M182" t="inlineStr">
+        <is>
+          <t>No hay nadie por la tarde</t>
+        </is>
+      </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -11260,7 +11236,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>HOSTELERIA</t>
+          <t>hosteleria</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -11319,12 +11295,12 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>HOSTELERIA</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>C/ General DÃ¡vila 4</t>
+          <t>C/ General Dávila 4</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -11344,7 +11320,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>sidreriaelpuerto183@movistar.es</t>
+          <t>info@sidreriaelpuerto.es</t>
         </is>
       </c>
       <c r="I184" s="2" t="n">
@@ -11363,11 +11339,7 @@
       <c r="L184" t="n">
         <v>5</v>
       </c>
-      <c r="M184" t="inlineStr">
-        <is>
-          <t>Cerrado en febrero</t>
-        </is>
-      </c>
+      <c r="M184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -11387,7 +11359,7 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>C/ Santa Lucía 30</t>
+          <t>C/ Santa LucÃ­a 30</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -11407,7 +11379,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>isabelquintana184@movistar.es</t>
+          <t>isabelquintana184@yahoo.es</t>
         </is>
       </c>
       <c r="I185" s="2" t="n">
@@ -11423,9 +11395,7 @@
           <t>domiciliado</t>
         </is>
       </c>
-      <c r="L185" t="n">
-        <v>0</v>
-      </c>
+      <c r="L185" t="inlineStr"/>
       <c r="M185" t="inlineStr"/>
     </row>
     <row r="186">
@@ -11436,7 +11406,7 @@
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>Antonio Gómez S.L.</t>
+          <t>A. GÃ³mez</t>
         </is>
       </c>
       <c r="C186" t="inlineStr">
@@ -11446,7 +11416,7 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Calle Peña Herbosa, 76</t>
+          <t>C/ PEÑA HERBOSA 76</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -11461,29 +11431,21 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>681 33 24 77</t>
-        </is>
-      </c>
-      <c r="H186" t="inlineStr">
-        <is>
-          <t>antoniogomezsl185@outlook.es</t>
-        </is>
-      </c>
+          <t>+34681332477</t>
+        </is>
+      </c>
+      <c r="H186" t="inlineStr"/>
       <c r="I186" s="2" t="n">
         <v>45524</v>
       </c>
-      <c r="J186" t="inlineStr">
-        <is>
-          <t>RUTA-3</t>
-        </is>
-      </c>
+      <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
           <t>domiciliado</t>
         </is>
       </c>
       <c r="L186" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="M186" t="inlineStr"/>
     </row>
@@ -11498,11 +11460,7 @@
           <t>José Bustamante</t>
         </is>
       </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Particular</t>
-        </is>
-      </c>
+      <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr">
         <is>
           <t>Avda. de los Castros 28</t>
@@ -11525,7 +11483,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>josebustamante186@outlook.es</t>
+          <t>josebustamante186@hotmail.com</t>
         </is>
       </c>
       <c r="I187" s="2" t="n">
@@ -11557,7 +11515,11 @@
           <t>Alberto Bustamante</t>
         </is>
       </c>
-      <c r="C188" t="inlineStr"/>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Particular</t>
+        </is>
+      </c>
       <c r="D188" t="inlineStr">
         <is>
           <t>C/ Santa Lucía 61</t>
@@ -11580,7 +11542,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t>albertobustamante187@outlook.es</t>
+          <t>albertobustamante187@telefonica.net</t>
         </is>
       </c>
       <c r="I188" s="2" t="n">
@@ -11609,7 +11571,7 @@
       </c>
       <c r="B189" t="inlineStr">
         <is>
-          <t>Rosa Fernández</t>
+          <t>Rosa FernÃ¡ndez</t>
         </is>
       </c>
       <c r="C189" t="inlineStr">
@@ -11619,7 +11581,7 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Avda. de España 57</t>
+          <t>Avda. de EspaÃ±a 57</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -11639,7 +11601,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>rosafernandez188@telefonica.net</t>
+          <t>rosafernandez188@yahoo.es</t>
         </is>
       </c>
       <c r="I189" s="2" t="n">
@@ -11658,11 +11620,7 @@
       <c r="L189" t="n">
         <v>0</v>
       </c>
-      <c r="M189" t="inlineStr">
-        <is>
-          <t>Preguntar por Charo</t>
-        </is>
-      </c>
+      <c r="M189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -11702,7 +11660,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>manuelpuente189@gmail.com</t>
+          <t>manuelpuente189@hotmail.com</t>
         </is>
       </c>
       <c r="I190" s="2" t="n">
@@ -11721,11 +11679,7 @@
       <c r="L190" t="n">
         <v>0</v>
       </c>
-      <c r="M190" t="inlineStr">
-        <is>
-          <t>No hay nadie por la tarde</t>
-        </is>
-      </c>
+      <c r="M190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -11740,7 +11694,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>HOSTELERIA</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D191" t="inlineStr">
@@ -11753,8 +11707,10 @@
           <t>Torrelavega</t>
         </is>
       </c>
-      <c r="F191" t="n">
-        <v>39300</v>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>39300</t>
+        </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
@@ -11778,11 +11734,7 @@
       <c r="L191" t="n">
         <v>3</v>
       </c>
-      <c r="M191" t="inlineStr">
-        <is>
-          <t>Cliente antiguo</t>
-        </is>
-      </c>
+      <c r="M191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -11797,7 +11749,7 @@
       </c>
       <c r="C192" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -11810,8 +11762,10 @@
           <t>Castro Urdiales</t>
         </is>
       </c>
-      <c r="F192" t="n">
-        <v>39700</v>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>39700</t>
+        </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
@@ -11875,11 +11829,7 @@
           <t>+34610099855</t>
         </is>
       </c>
-      <c r="H193" t="inlineStr">
-        <is>
-          <t>hotelsantaana192@hotmail.com</t>
-        </is>
-      </c>
+      <c r="H193" t="inlineStr"/>
       <c r="I193" s="2" t="n">
         <v>42323</v>
       </c>
@@ -11934,11 +11884,7 @@
           <t>942 97 38 72</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
-        <is>
-          <t>elenagomez193@movistar.es</t>
-        </is>
-      </c>
+      <c r="H194" t="inlineStr"/>
       <c r="I194" s="2" t="n">
         <v>43552</v>
       </c>
@@ -11957,7 +11903,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Cliente antiguo</t>
+          <t>Preguntar por Charo</t>
         </is>
       </c>
     </row>
@@ -11974,7 +11920,7 @@
       </c>
       <c r="C195" t="inlineStr">
         <is>
-          <t>HOSTELERIA</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -11999,7 +11945,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>pensionlaplaza194@telefonica.net</t>
+          <t>pensionlaplaza194@yahoo.es</t>
         </is>
       </c>
       <c r="I195" s="2" t="n">
@@ -12033,7 +11979,7 @@
       </c>
       <c r="C196" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -12058,7 +12004,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>fernandoescalante195@yahoo.es</t>
+          <t>fernandoescalante195@hotmail.com</t>
         </is>
       </c>
       <c r="I196" s="2" t="n">
@@ -12077,11 +12023,7 @@
       <c r="L196" t="n">
         <v>3</v>
       </c>
-      <c r="M196" t="inlineStr">
-        <is>
-          <t>Abre solo fines de semana en invierno</t>
-        </is>
-      </c>
+      <c r="M196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -12096,7 +12038,7 @@
       </c>
       <c r="C197" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -12121,7 +12063,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>info@asadorlaterraza.es</t>
+          <t>asadorlaterraza196@movistar.es</t>
         </is>
       </c>
       <c r="I197" s="2" t="n">
@@ -12180,7 +12122,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>juanceballos197@hotmail.com</t>
+          <t>juanceballos197@telefonica.net</t>
         </is>
       </c>
       <c r="I198" s="2" t="n">
@@ -12196,12 +12138,10 @@
           <t>domiciliado</t>
         </is>
       </c>
-      <c r="L198" t="n">
-        <v>0</v>
-      </c>
+      <c r="L198" t="inlineStr"/>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Preguntar por Charo</t>
+          <t>Cliente antiguo</t>
         </is>
       </c>
     </row>
@@ -12241,11 +12181,7 @@
           <t>942 10 89 95</t>
         </is>
       </c>
-      <c r="H199" t="inlineStr">
-        <is>
-          <t>info@sidreriaeltonel.es</t>
-        </is>
-      </c>
+      <c r="H199" t="inlineStr"/>
       <c r="I199" s="2" t="n">
         <v>43556</v>
       </c>
@@ -12275,7 +12211,11 @@
           <t>Javier Ibáñez</t>
         </is>
       </c>
-      <c r="C200" t="inlineStr"/>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>part.</t>
+        </is>
+      </c>
       <c r="D200" t="inlineStr">
         <is>
           <t>Barrio El Cruce 56</t>
@@ -12315,7 +12255,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Descarga complicada, calle estrecha</t>
+          <t>Llamar antes de ir</t>
         </is>
       </c>
     </row>
@@ -12330,7 +12270,11 @@
           <t>Restaurante Casa Elena</t>
         </is>
       </c>
-      <c r="C201" t="inlineStr"/>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>hosteleria</t>
+        </is>
+      </c>
       <c r="D201" t="inlineStr">
         <is>
           <t>Barrio Somahoz 40</t>
@@ -12353,17 +12297,13 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>info@restaurantecasaele.es</t>
+          <t>restaurantecasaelena200@movistar.es</t>
         </is>
       </c>
       <c r="I201" s="2" t="n">
         <v>42208</v>
       </c>
-      <c r="J201" t="inlineStr">
-        <is>
-          <t>RUTA-4</t>
-        </is>
-      </c>
+      <c r="J201" t="inlineStr"/>
       <c r="K201" t="inlineStr">
         <is>
           <t>efectivo</t>
@@ -12374,7 +12314,7 @@
       </c>
       <c r="M201" t="inlineStr">
         <is>
-          <t>Cerrado los lunes</t>
+          <t>Entrar por la parte de atrás</t>
         </is>
       </c>
     </row>
@@ -12404,10 +12344,8 @@
           <t>Torrelavega</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
-        <is>
-          <t>39300</t>
-        </is>
+      <c r="F202" t="n">
+        <v>39300</v>
       </c>
       <c r="G202" t="inlineStr">
         <is>
@@ -12416,7 +12354,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>miguelmazo201@telefonica.net</t>
+          <t>miguelmazo201@gmail.com</t>
         </is>
       </c>
       <c r="I202" s="2" t="n">
@@ -12450,7 +12388,7 @@
       </c>
       <c r="C203" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -12494,7 +12432,11 @@
       <c r="L203" t="n">
         <v>5</v>
       </c>
-      <c r="M203" t="inlineStr"/>
+      <c r="M203" t="inlineStr">
+        <is>
+          <t>Llamar antes de ir</t>
+        </is>
+      </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -12509,7 +12451,7 @@
       </c>
       <c r="C204" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -12534,7 +12476,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>luciacuadrado203@outlook.es</t>
+          <t>luciacuadrado203@telefonica.net</t>
         </is>
       </c>
       <c r="I204" s="2" t="n">
@@ -12553,7 +12495,11 @@
       <c r="L204" t="n">
         <v>0</v>
       </c>
-      <c r="M204" t="inlineStr"/>
+      <c r="M204" t="inlineStr">
+        <is>
+          <t>Llamar antes de ir</t>
+        </is>
+      </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -12568,7 +12514,7 @@
       </c>
       <c r="C205" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -12593,7 +12539,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>carloscorral204@movistar.es</t>
+          <t>carloscorral204@yahoo.es</t>
         </is>
       </c>
       <c r="I205" s="2" t="n">
@@ -12627,7 +12573,7 @@
       </c>
       <c r="C206" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -12650,7 +12596,11 @@
           <t>985 04 47 76</t>
         </is>
       </c>
-      <c r="H206" t="inlineStr"/>
+      <c r="H206" t="inlineStr">
+        <is>
+          <t>fernandoceballos205@yahoo.es</t>
+        </is>
+      </c>
       <c r="I206" s="2" t="n">
         <v>43707</v>
       </c>
@@ -12664,7 +12614,9 @@
           <t>transferencia</t>
         </is>
       </c>
-      <c r="L206" t="inlineStr"/>
+      <c r="L206" t="n">
+        <v>0</v>
+      </c>
       <c r="M206" t="inlineStr"/>
     </row>
     <row r="207">
@@ -12764,7 +12716,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>chiringuitoelrincon207@hotmail.com</t>
+          <t>info@chiringuitoelrinco.es</t>
         </is>
       </c>
       <c r="I208" s="2" t="n">
@@ -12823,7 +12775,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>sergiopuente208@movistar.es</t>
+          <t>sergiopuente208@telefonica.net</t>
         </is>
       </c>
       <c r="I209" s="2" t="n">
@@ -12842,7 +12794,11 @@
       <c r="L209" t="n">
         <v>0</v>
       </c>
-      <c r="M209" t="inlineStr"/>
+      <c r="M209" t="inlineStr">
+        <is>
+          <t>El reparto pasa sobre las 7 y media</t>
+        </is>
+      </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -12852,7 +12808,7 @@
       </c>
       <c r="B210" t="inlineStr">
         <is>
-          <t>Iván Quintana</t>
+          <t>IvÃ¡n Quintana</t>
         </is>
       </c>
       <c r="C210" t="inlineStr">
@@ -12882,7 +12838,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>ivanquintana209@movistar.es</t>
+          <t>ivanquintana209@outlook.es</t>
         </is>
       </c>
       <c r="I210" s="2" t="n">
@@ -12901,7 +12857,11 @@
       <c r="L210" t="n">
         <v>0</v>
       </c>
-      <c r="M210" t="inlineStr"/>
+      <c r="M210" t="inlineStr">
+        <is>
+          <t>Ojo con la factura</t>
+        </is>
+      </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -12941,7 +12901,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>ivannoriega210@gmail.com</t>
+          <t>ivannoriega210@movistar.es</t>
         </is>
       </c>
       <c r="I211" s="2" t="n">
@@ -13019,7 +12979,11 @@
       <c r="L212" t="n">
         <v>0</v>
       </c>
-      <c r="M212" t="inlineStr"/>
+      <c r="M212" t="inlineStr">
+        <is>
+          <t>Cerrado en febrero</t>
+        </is>
+      </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
@@ -13039,7 +13003,7 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>C/ Peña Herbosa 17</t>
+          <t>C/ PeÃ±a Herbosa 17</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -13075,9 +13039,7 @@
           <t>domiciliado</t>
         </is>
       </c>
-      <c r="L213" t="n">
-        <v>0</v>
-      </c>
+      <c r="L213" t="inlineStr"/>
       <c r="M213" t="inlineStr"/>
     </row>
     <row r="214">
@@ -13093,7 +13055,7 @@
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -13106,8 +13068,10 @@
           <t>Llanes</t>
         </is>
       </c>
-      <c r="F214" t="n">
-        <v>33500</v>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>33500</t>
+        </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
@@ -13116,7 +13080,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>rosavillegas213@outlook.es</t>
+          <t>rosavillegas213@gmail.com</t>
         </is>
       </c>
       <c r="I214" s="2" t="n">
@@ -13135,11 +13099,7 @@
       <c r="L214" t="n">
         <v>0</v>
       </c>
-      <c r="M214" t="inlineStr">
-        <is>
-          <t>No hay nadie por la tarde</t>
-        </is>
-      </c>
+      <c r="M214" t="inlineStr"/>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
@@ -13154,7 +13114,7 @@
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -13179,7 +13139,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>carmenruiz214@hotmail.com</t>
+          <t>carmenruiz214@gmail.com</t>
         </is>
       </c>
       <c r="I215" s="2" t="n">
@@ -13198,7 +13158,11 @@
       <c r="L215" t="n">
         <v>0</v>
       </c>
-      <c r="M215" t="inlineStr"/>
+      <c r="M215" t="inlineStr">
+        <is>
+          <t>Abre solo fines de semana en invierno</t>
+        </is>
+      </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
@@ -13238,7 +13202,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>carlosceballos215@movistar.es</t>
+          <t>carlosceballos215@telefonica.net</t>
         </is>
       </c>
       <c r="I216" s="2" t="n">
@@ -13267,7 +13231,7 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>RubÃ©n Puente</t>
+          <t>Rubén Puente</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -13297,7 +13261,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>rubenpuente216@yahoo.es</t>
+          <t>rubenpuente216@telefonica.net</t>
         </is>
       </c>
       <c r="I217" s="2" t="n">
@@ -13316,11 +13280,7 @@
       <c r="L217" t="n">
         <v>0</v>
       </c>
-      <c r="M217" t="inlineStr">
-        <is>
-          <t>Abre solo fines de semana en invierno</t>
-        </is>
-      </c>
+      <c r="M217" t="inlineStr"/>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
@@ -13360,7 +13320,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>asadorelmolino217@yahoo.es</t>
+          <t>asadorelmolino217@outlook.es</t>
         </is>
       </c>
       <c r="I218" s="2" t="n">
@@ -13381,7 +13341,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Abre solo fines de semana en invierno</t>
+          <t>Entrar por la parte de atrás</t>
         </is>
       </c>
     </row>
@@ -13398,12 +13358,12 @@
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>hosteleria</t>
         </is>
       </c>
       <c r="D219" t="inlineStr">
         <is>
-          <t>C/ General Dávila 18</t>
+          <t>C/ General DÃ¡vila 18</t>
         </is>
       </c>
       <c r="E219" t="inlineStr">
@@ -13457,7 +13417,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -13480,7 +13440,11 @@
           <t>619-24-88-82</t>
         </is>
       </c>
-      <c r="H220" t="inlineStr"/>
+      <c r="H220" t="inlineStr">
+        <is>
+          <t>mesonelmirador219@hotmail.com</t>
+        </is>
+      </c>
       <c r="I220" s="2" t="n">
         <v>45328</v>
       </c>
@@ -13512,7 +13476,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -13537,7 +13501,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>rubenposada220@yahoo.es</t>
+          <t>rubenposada220@gmail.com</t>
         </is>
       </c>
       <c r="I221" s="2" t="n">
@@ -13556,11 +13520,7 @@
       <c r="L221" t="n">
         <v>0</v>
       </c>
-      <c r="M221" t="inlineStr">
-        <is>
-          <t>Cliente antiguo</t>
-        </is>
-      </c>
+      <c r="M221" t="inlineStr"/>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
@@ -13570,7 +13530,7 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>Nuria Lavín</t>
+          <t>Nuria LavÃ­n</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
@@ -13598,11 +13558,7 @@
           <t>942422733</t>
         </is>
       </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>nurialavin221@outlook.es</t>
-        </is>
-      </c>
+      <c r="H222" t="inlineStr"/>
       <c r="I222" s="2" t="n">
         <v>42595</v>
       </c>
@@ -13629,12 +13585,12 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>Ãscar GutiÃ©rrez</t>
+          <t>Óscar Gutiérrez</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -13657,7 +13613,11 @@
           <t>722403552</t>
         </is>
       </c>
-      <c r="H223" t="inlineStr"/>
+      <c r="H223" t="inlineStr">
+        <is>
+          <t>oscargutierrez222@gmail.com</t>
+        </is>
+      </c>
       <c r="I223" s="2" t="n">
         <v>42614</v>
       </c>
@@ -13674,11 +13634,7 @@
       <c r="L223" t="n">
         <v>0</v>
       </c>
-      <c r="M223" t="inlineStr">
-        <is>
-          <t>Llamar antes de ir</t>
-        </is>
-      </c>
+      <c r="M223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
@@ -13688,10 +13644,14 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>Pensión El Cantábrico</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr"/>
+          <t>PensiÃ³n El CantÃ¡brico</t>
+        </is>
+      </c>
+      <c r="C224" t="inlineStr">
+        <is>
+          <t>Hostelería</t>
+        </is>
+      </c>
       <c r="D224" t="inlineStr">
         <is>
           <t>C/ Ruamayor 44</t>
@@ -13730,9 +13690,7 @@
           <t>efectivo</t>
         </is>
       </c>
-      <c r="L224" t="n">
-        <v>0</v>
-      </c>
+      <c r="L224" t="inlineStr"/>
       <c r="M224" t="inlineStr"/>
     </row>
     <row r="225">
@@ -13773,7 +13731,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t>nuriaortiz224@yahoo.es</t>
+          <t>nuriaortiz224@gmail.com</t>
         </is>
       </c>
       <c r="I225" s="2" t="n">
@@ -13807,7 +13765,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
@@ -13820,21 +13778,15 @@
           <t>Torrelavega</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
-        <is>
-          <t>39300</t>
-        </is>
+      <c r="F226" t="n">
+        <v>39300</v>
       </c>
       <c r="G226" t="inlineStr">
         <is>
           <t>942 13 14 08</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>nuriacobo225@gmail.com</t>
-        </is>
-      </c>
+      <c r="H226" t="inlineStr"/>
       <c r="I226" s="2" t="n">
         <v>45375</v>
       </c>
@@ -13851,7 +13803,11 @@
       <c r="L226" t="n">
         <v>0</v>
       </c>
-      <c r="M226" t="inlineStr"/>
+      <c r="M226" t="inlineStr">
+        <is>
+          <t>Cambió de dueño en 2023</t>
+        </is>
+      </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
@@ -13889,7 +13845,11 @@
           <t>942989902</t>
         </is>
       </c>
-      <c r="H227" t="inlineStr"/>
+      <c r="H227" t="inlineStr">
+        <is>
+          <t>pizzerialabodega226@telefonica.net</t>
+        </is>
+      </c>
       <c r="I227" s="2" t="n">
         <v>44663</v>
       </c>
@@ -13921,7 +13881,7 @@
       </c>
       <c r="C228" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>hosteleria</t>
         </is>
       </c>
       <c r="D228" t="inlineStr">
@@ -14005,7 +13965,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>oscarnoriega228@telefonica.net</t>
+          <t>oscarnoriega228@hotmail.com</t>
         </is>
       </c>
       <c r="I229" s="2" t="n">
@@ -14024,7 +13984,11 @@
       <c r="L229" t="n">
         <v>0</v>
       </c>
-      <c r="M229" t="inlineStr"/>
+      <c r="M229" t="inlineStr">
+        <is>
+          <t>Paga a 30 días</t>
+        </is>
+      </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
@@ -14052,19 +14016,17 @@
           <t>Camargo</t>
         </is>
       </c>
-      <c r="F230" t="n">
-        <v>39600</v>
+      <c r="F230" t="inlineStr">
+        <is>
+          <t>39600</t>
+        </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
           <t>722-93-71-46</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
-        <is>
-          <t>ivanlavin229@hotmail.com</t>
-        </is>
-      </c>
+      <c r="H230" t="inlineStr"/>
       <c r="I230" s="2" t="n">
         <v>44978</v>
       </c>
@@ -14078,14 +14040,8 @@
           <t>domiciliado</t>
         </is>
       </c>
-      <c r="L230" t="n">
-        <v>0</v>
-      </c>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>Cambió de dueño en 2023</t>
-        </is>
-      </c>
+      <c r="L230" t="inlineStr"/>
+      <c r="M230" t="inlineStr"/>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
@@ -14144,7 +14100,11 @@
       <c r="L231" t="n">
         <v>0</v>
       </c>
-      <c r="M231" t="inlineStr"/>
+      <c r="M231" t="inlineStr">
+        <is>
+          <t>Cerrado los lunes</t>
+        </is>
+      </c>
     </row>
     <row r="232">
       <c r="A232" t="inlineStr">
@@ -14154,7 +14114,7 @@
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>Ana Sáiz</t>
+          <t>Ana SÃ¡iz</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -14182,30 +14142,20 @@
           <t>674391716</t>
         </is>
       </c>
-      <c r="H232" t="inlineStr">
-        <is>
-          <t>anasaiz231@yahoo.es</t>
-        </is>
-      </c>
+      <c r="H232" t="inlineStr"/>
       <c r="I232" s="2" t="n">
         <v>42334</v>
       </c>
-      <c r="J232" t="inlineStr">
-        <is>
-          <t>RUTA-1</t>
-        </is>
-      </c>
+      <c r="J232" t="inlineStr"/>
       <c r="K232" t="inlineStr">
         <is>
           <t>domiciliado</t>
         </is>
       </c>
-      <c r="L232" t="inlineStr"/>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>Cerrado en febrero</t>
-        </is>
-      </c>
+      <c r="L232" t="n">
+        <v>0</v>
+      </c>
+      <c r="M232" t="inlineStr"/>
     </row>
     <row r="233">
       <c r="A233" t="inlineStr">
@@ -14245,7 +14195,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>pilargutierrez232@gmail.com</t>
+          <t>pilargutierrez232@telefonica.net</t>
         </is>
       </c>
       <c r="I233" s="2" t="n">
@@ -14261,7 +14211,9 @@
           <t>transferencia</t>
         </is>
       </c>
-      <c r="L233" t="inlineStr"/>
+      <c r="L233" t="n">
+        <v>0</v>
+      </c>
       <c r="M233" t="inlineStr"/>
     </row>
     <row r="234">
@@ -14277,7 +14229,7 @@
       </c>
       <c r="C234" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D234" t="inlineStr">
@@ -14302,7 +14254,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t>mesoncasaramon233@gmail.com</t>
+          <t>info@mesoncasaramon.es</t>
         </is>
       </c>
       <c r="I234" s="2" t="n">
@@ -14361,7 +14313,7 @@
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>sidreriaelcruce234@outlook.es</t>
+          <t>info@sidreriaelcruce.es</t>
         </is>
       </c>
       <c r="I235" s="2" t="n">
@@ -14380,7 +14332,11 @@
       <c r="L235" t="n">
         <v>0</v>
       </c>
-      <c r="M235" t="inlineStr"/>
+      <c r="M235" t="inlineStr">
+        <is>
+          <t>Paga a 30 días</t>
+        </is>
+      </c>
     </row>
     <row r="236">
       <c r="A236" t="inlineStr">
@@ -14395,7 +14351,7 @@
       </c>
       <c r="C236" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D236" t="inlineStr">
@@ -14420,7 +14376,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t>info@barlafuente.es</t>
+          <t>barlafuente235@telefonica.net</t>
         </is>
       </c>
       <c r="I236" s="2" t="n">
@@ -14452,11 +14408,7 @@
           <t>Pedro Noriega</t>
         </is>
       </c>
-      <c r="C237" t="inlineStr">
-        <is>
-          <t>part.</t>
-        </is>
-      </c>
+      <c r="C237" t="inlineStr"/>
       <c r="D237" t="inlineStr">
         <is>
           <t>Barrio La Iglesia 47</t>
@@ -14467,15 +14419,21 @@
           <t>Llanes</t>
         </is>
       </c>
-      <c r="F237" t="n">
-        <v>33500</v>
+      <c r="F237" t="inlineStr">
+        <is>
+          <t>33500</t>
+        </is>
       </c>
       <c r="G237" t="inlineStr">
         <is>
           <t>639 73 40 49</t>
         </is>
       </c>
-      <c r="H237" t="inlineStr"/>
+      <c r="H237" t="inlineStr">
+        <is>
+          <t>pedronoriega236@telefonica.net</t>
+        </is>
+      </c>
       <c r="I237" s="2" t="n">
         <v>43621</v>
       </c>
@@ -14532,7 +14490,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t>beatrizgutierrez237@outlook.es</t>
+          <t>beatrizgutierrez237@movistar.es</t>
         </is>
       </c>
       <c r="I238" s="2" t="n">
@@ -14561,17 +14519,17 @@
       </c>
       <c r="B239" t="inlineStr">
         <is>
-          <t>Patricia Salces S.L.</t>
+          <t>PATRICIA SALCES</t>
         </is>
       </c>
       <c r="C239" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D239" t="inlineStr">
         <is>
-          <t>C/ RUAMAYOR 50</t>
+          <t>Calle Ruamayor 50</t>
         </is>
       </c>
       <c r="E239" t="inlineStr">
@@ -14586,12 +14544,12 @@
       </c>
       <c r="G239" t="inlineStr">
         <is>
-          <t>942-17-66-95</t>
+          <t>942 17 66 95</t>
         </is>
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>patriciasalcessl238@movistar.es</t>
+          <t>patriciasalces238@telefonica.net</t>
         </is>
       </c>
       <c r="I239" s="2" t="n">
@@ -14623,11 +14581,7 @@
           <t>Elena Ceballos</t>
         </is>
       </c>
-      <c r="C240" t="inlineStr">
-        <is>
-          <t>part.</t>
-        </is>
-      </c>
+      <c r="C240" t="inlineStr"/>
       <c r="D240" t="inlineStr">
         <is>
           <t>Pº de Pereda 72</t>
@@ -14648,7 +14602,11 @@
           <t>985-72-89-97</t>
         </is>
       </c>
-      <c r="H240" t="inlineStr"/>
+      <c r="H240" t="inlineStr">
+        <is>
+          <t>elenaceballos239@hotmail.com</t>
+        </is>
+      </c>
       <c r="I240" s="2" t="n">
         <v>43538</v>
       </c>
@@ -14665,11 +14623,7 @@
       <c r="L240" t="n">
         <v>0</v>
       </c>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>Abre solo fines de semana en invierno</t>
-        </is>
-      </c>
+      <c r="M240" t="inlineStr"/>
     </row>
     <row r="241">
       <c r="A241" t="inlineStr">
@@ -14679,12 +14633,12 @@
       </c>
       <c r="B241" t="inlineStr">
         <is>
-          <t>JosÃ© Ruiz</t>
+          <t>José Ruiz</t>
         </is>
       </c>
       <c r="C241" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D241" t="inlineStr">
@@ -14707,7 +14661,11 @@
           <t>942629693</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr"/>
+      <c r="H241" t="inlineStr">
+        <is>
+          <t>joseruiz240@outlook.es</t>
+        </is>
+      </c>
       <c r="I241" s="2" t="n">
         <v>42253</v>
       </c>
@@ -14752,10 +14710,8 @@
           <t>Torrelavega</t>
         </is>
       </c>
-      <c r="F242" t="inlineStr">
-        <is>
-          <t>39300</t>
-        </is>
+      <c r="F242" t="n">
+        <v>39300</v>
       </c>
       <c r="G242" t="inlineStr">
         <is>
@@ -14776,10 +14732,12 @@
           <t>domiciliado</t>
         </is>
       </c>
-      <c r="L242" t="n">
-        <v>0</v>
-      </c>
-      <c r="M242" t="inlineStr"/>
+      <c r="L242" t="inlineStr"/>
+      <c r="M242" t="inlineStr">
+        <is>
+          <t>Solo garrafas</t>
+        </is>
+      </c>
     </row>
     <row r="243">
       <c r="A243" t="inlineStr">
@@ -14819,7 +14777,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t>carmencuadrado242@gmail.com</t>
+          <t>carmencuadrado242@hotmail.com</t>
         </is>
       </c>
       <c r="I243" s="2" t="n">
@@ -14838,11 +14796,7 @@
       <c r="L243" t="n">
         <v>0</v>
       </c>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>Pide albarán siempre</t>
-        </is>
-      </c>
+      <c r="M243" t="inlineStr"/>
     </row>
     <row r="244">
       <c r="A244" t="inlineStr">
@@ -14882,7 +14836,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>anaruiz243@yahoo.es</t>
+          <t>anaruiz243@gmail.com</t>
         </is>
       </c>
       <c r="I244" s="2" t="n">
@@ -14916,7 +14870,7 @@
       </c>
       <c r="C245" t="inlineStr">
         <is>
-          <t>HOSTELERIA</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D245" t="inlineStr">
@@ -14941,7 +14895,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>chiringuitocasaaurora244@movistar.es</t>
+          <t>info@chiringuitocasaaur.es</t>
         </is>
       </c>
       <c r="I245" s="2" t="n">
@@ -14975,7 +14929,7 @@
       </c>
       <c r="C246" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D246" t="inlineStr">
@@ -14998,7 +14952,11 @@
           <t>652815877</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr"/>
+      <c r="H246" t="inlineStr">
+        <is>
+          <t>rosapuente245@hotmail.com</t>
+        </is>
+      </c>
       <c r="I246" s="2" t="n">
         <v>45036</v>
       </c>
@@ -15017,7 +14975,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Pide albarán siempre</t>
+          <t>El reparto pasa sobre las 7 y media</t>
         </is>
       </c>
     </row>
@@ -15034,7 +14992,7 @@
       </c>
       <c r="C247" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D247" t="inlineStr">
@@ -15059,7 +15017,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>sergiobolado246@yahoo.es</t>
+          <t>sergiobolado246.yahoo.es</t>
         </is>
       </c>
       <c r="I247" s="2" t="n">
@@ -15106,21 +15064,15 @@
           <t>Ribadesella</t>
         </is>
       </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>33560</t>
-        </is>
+      <c r="F248" t="n">
+        <v>33560</v>
       </c>
       <c r="G248" t="inlineStr">
         <is>
           <t>942232423</t>
         </is>
       </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>fernandosalces247@outlook.es</t>
-        </is>
-      </c>
+      <c r="H248" t="inlineStr"/>
       <c r="I248" s="2" t="n">
         <v>44134</v>
       </c>
@@ -15152,7 +15104,7 @@
       </c>
       <c r="C249" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D249" t="inlineStr">
@@ -15177,7 +15129,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t>pizzerialapalma248@gmail.com</t>
+          <t>info@pizzerialapalma.es</t>
         </is>
       </c>
       <c r="I249" s="2" t="n">
@@ -15196,11 +15148,7 @@
       <c r="L249" t="n">
         <v>8</v>
       </c>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>Cerrado los lunes</t>
-        </is>
-      </c>
+      <c r="M249" t="inlineStr"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -15215,7 +15163,7 @@
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D250" t="inlineStr">
@@ -15235,12 +15183,16 @@
       </c>
       <c r="G250" t="inlineStr">
         <is>
-          <t>637664533</t>
-        </is>
-      </c>
-      <c r="H250" t="inlineStr"/>
+          <t>+34637664533</t>
+        </is>
+      </c>
+      <c r="H250" t="inlineStr">
+        <is>
+          <t>pensioncasapepe249@gmail.com</t>
+        </is>
+      </c>
       <c r="I250" s="2" t="n">
-        <v>44713</v>
+        <v>43773</v>
       </c>
       <c r="J250" t="inlineStr">
         <is>
@@ -15268,7 +15220,11 @@
           <t>Pedro Setién</t>
         </is>
       </c>
-      <c r="C251" t="inlineStr"/>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Particular</t>
+        </is>
+      </c>
       <c r="D251" t="inlineStr">
         <is>
           <t>Avda. de España 29</t>
@@ -15289,7 +15245,11 @@
           <t>+34985829755</t>
         </is>
       </c>
-      <c r="H251" t="inlineStr"/>
+      <c r="H251" t="inlineStr">
+        <is>
+          <t>pedrosetien250@telefonica.net</t>
+        </is>
+      </c>
       <c r="I251" s="2" t="n">
         <v>42433</v>
       </c>
@@ -15362,9 +15322,7 @@
           <t>domiciliado</t>
         </is>
       </c>
-      <c r="L252" t="n">
-        <v>0</v>
-      </c>
+      <c r="L252" t="inlineStr"/>
       <c r="M252" t="inlineStr"/>
     </row>
     <row r="253">
@@ -15380,12 +15338,12 @@
       </c>
       <c r="C253" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D253" t="inlineStr">
         <is>
-          <t>C/ Santa Lucía 82</t>
+          <t>C/ Santa LucÃ­a 82</t>
         </is>
       </c>
       <c r="E253" t="inlineStr">
@@ -15405,7 +15363,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t>rubengomez252@movistar.es</t>
+          <t>rubengomez252@hotmail.com</t>
         </is>
       </c>
       <c r="I253" s="2" t="n">
@@ -15434,12 +15392,12 @@
       </c>
       <c r="B254" t="inlineStr">
         <is>
-          <t>Cafetería El Cantón</t>
+          <t>CafeterÃ­a El CantÃ³n</t>
         </is>
       </c>
       <c r="C254" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D254" t="inlineStr">
@@ -15464,7 +15422,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t>info@cafeteriaelcanton.es</t>
+          <t>cafeteriaelcanton253@gmail.com</t>
         </is>
       </c>
       <c r="I254" s="2" t="n">
@@ -15498,7 +15456,7 @@
       </c>
       <c r="C255" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D255" t="inlineStr">
@@ -15542,11 +15500,7 @@
       <c r="L255" t="n">
         <v>0</v>
       </c>
-      <c r="M255" t="inlineStr">
-        <is>
-          <t>Paga a 30 días</t>
-        </is>
-      </c>
+      <c r="M255" t="inlineStr"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -15561,12 +15515,12 @@
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D256" t="inlineStr">
         <is>
-          <t>C/ del Río 36</t>
+          <t>C/ del RÃ­o 36</t>
         </is>
       </c>
       <c r="E256" t="inlineStr">
@@ -15586,7 +15540,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>nuriabolado255@telefonica.net</t>
+          <t>nuriabolado255@gmail.com</t>
         </is>
       </c>
       <c r="I256" s="2" t="n">
@@ -15602,7 +15556,9 @@
           <t>transferencia</t>
         </is>
       </c>
-      <c r="L256" t="inlineStr"/>
+      <c r="L256" t="n">
+        <v>0</v>
+      </c>
       <c r="M256" t="inlineStr"/>
     </row>
     <row r="257">
@@ -15613,12 +15569,12 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>Marisquería Casa Nieves</t>
+          <t>MarisquerÃ­a Casa Nieves</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D257" t="inlineStr">
@@ -15641,11 +15597,7 @@
           <t>657428919</t>
         </is>
       </c>
-      <c r="H257" t="inlineStr">
-        <is>
-          <t>info@marisqueriacasanie.es</t>
-        </is>
-      </c>
+      <c r="H257" t="inlineStr"/>
       <c r="I257" s="2" t="n">
         <v>44843</v>
       </c>
@@ -15700,11 +15652,7 @@
           <t>942-47-97-26</t>
         </is>
       </c>
-      <c r="H258" t="inlineStr">
-        <is>
-          <t>restauranteelcantabric257@yahoo.es</t>
-        </is>
-      </c>
+      <c r="H258" t="inlineStr"/>
       <c r="I258" s="2" t="n">
         <v>42209</v>
       </c>
@@ -15721,11 +15669,7 @@
       <c r="L258" t="n">
         <v>10</v>
       </c>
-      <c r="M258" t="inlineStr">
-        <is>
-          <t>Descarga complicada, calle estrecha</t>
-        </is>
-      </c>
+      <c r="M258" t="inlineStr"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -15735,17 +15679,17 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>PIZZERÍA LA TERRAZA</t>
+          <t>La Terraza, Pizzería</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>HOSTELERIA</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D259" t="inlineStr">
         <is>
-          <t>C/ Cervantes, 41</t>
+          <t>C/ CERVANTES 41</t>
         </is>
       </c>
       <c r="E259" t="inlineStr">
@@ -15753,19 +15697,17 @@
           <t>Comillas</t>
         </is>
       </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>39520</t>
-        </is>
+      <c r="F259" t="n">
+        <v>39520</v>
       </c>
       <c r="G259" t="inlineStr">
         <is>
-          <t>722 75 88 66</t>
+          <t>722-75-88-66</t>
         </is>
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>info@pizzerialaterraza.es</t>
+          <t>info@laterrazapizzeria.es</t>
         </is>
       </c>
       <c r="I259" s="2" t="n">
@@ -15799,7 +15741,7 @@
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D260" t="inlineStr">
@@ -15822,7 +15764,11 @@
           <t>942-87-94-38</t>
         </is>
       </c>
-      <c r="H260" t="inlineStr"/>
+      <c r="H260" t="inlineStr">
+        <is>
+          <t>oscardiego259@outlook.es</t>
+        </is>
+      </c>
       <c r="I260" s="2" t="n">
         <v>43017</v>
       </c>
@@ -15839,7 +15785,11 @@
       <c r="L260" t="n">
         <v>0</v>
       </c>
-      <c r="M260" t="inlineStr"/>
+      <c r="M260" t="inlineStr">
+        <is>
+          <t>Tiene fuente en alquiler</t>
+        </is>
+      </c>
     </row>
     <row r="261">
       <c r="A261" t="inlineStr">
@@ -15849,12 +15799,12 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>Pensión Santa Ana</t>
+          <t>PensiÃ³n Santa Ana</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D261" t="inlineStr">
@@ -15898,11 +15848,7 @@
       <c r="L261" t="n">
         <v>8</v>
       </c>
-      <c r="M261" t="inlineStr">
-        <is>
-          <t>Cerrado en febrero</t>
-        </is>
-      </c>
+      <c r="M261" t="inlineStr"/>
     </row>
     <row r="262">
       <c r="A262" t="inlineStr">
@@ -15917,7 +15863,7 @@
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D262" t="inlineStr">
@@ -15942,7 +15888,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>fernandohiguera261@movistar.es</t>
+          <t>fernandohiguera261@outlook.es</t>
         </is>
       </c>
       <c r="I262" s="2" t="n">
@@ -15961,7 +15907,11 @@
       <c r="L262" t="n">
         <v>0</v>
       </c>
-      <c r="M262" t="inlineStr"/>
+      <c r="M262" t="inlineStr">
+        <is>
+          <t>Preguntar por Charo</t>
+        </is>
+      </c>
     </row>
     <row r="263">
       <c r="A263" t="inlineStr">
@@ -15976,7 +15926,7 @@
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D263" t="inlineStr">
@@ -16001,7 +15951,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t>sidreriaelrincon262@yahoo.es</t>
+          <t>info@sidreriaelrincon.es</t>
         </is>
       </c>
       <c r="I263" s="2" t="n">
@@ -16017,12 +15967,10 @@
           <t>domiciliado</t>
         </is>
       </c>
-      <c r="L263" t="inlineStr"/>
-      <c r="M263" t="inlineStr">
-        <is>
-          <t>Preguntar por Charo</t>
-        </is>
-      </c>
+      <c r="L263" t="n">
+        <v>0</v>
+      </c>
+      <c r="M263" t="inlineStr"/>
     </row>
     <row r="264">
       <c r="A264" t="inlineStr">
@@ -16037,7 +15985,7 @@
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>hosteleria</t>
         </is>
       </c>
       <c r="D264" t="inlineStr">
@@ -16060,11 +16008,7 @@
           <t>942-96-06-70</t>
         </is>
       </c>
-      <c r="H264" t="inlineStr">
-        <is>
-          <t>info@chiringuitolagavio.es</t>
-        </is>
-      </c>
+      <c r="H264" t="inlineStr"/>
       <c r="I264" s="2" t="n">
         <v>44133</v>
       </c>
@@ -16121,7 +16065,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>patriciacarrera264@telefonica.net</t>
+          <t>patriciacarrera264@movistar.es</t>
         </is>
       </c>
       <c r="I265" s="2" t="n">
@@ -16150,17 +16094,17 @@
       </c>
       <c r="B266" t="inlineStr">
         <is>
-          <t>PILAR CORRAL S.L.</t>
+          <t>Corral, Pilar</t>
         </is>
       </c>
       <c r="C266" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D266" t="inlineStr">
         <is>
-          <t>Calle Alta 13</t>
+          <t>C/ Alta nº 13</t>
         </is>
       </c>
       <c r="E266" t="inlineStr">
@@ -16175,16 +16119,16 @@
       </c>
       <c r="G266" t="inlineStr">
         <is>
-          <t>942-64-82-57</t>
+          <t>942648257</t>
         </is>
       </c>
       <c r="H266" t="inlineStr">
         <is>
-          <t>pilarcorralsl265@hotmail.com</t>
+          <t>corralpilar265@yahoo.es</t>
         </is>
       </c>
       <c r="I266" s="2" t="n">
-        <v>44520</v>
+        <v>43001</v>
       </c>
       <c r="J266" t="inlineStr">
         <is>
@@ -16197,11 +16141,11 @@
         </is>
       </c>
       <c r="L266" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Preguntar por Charo</t>
+          <t>Cambió de dueño en 2023</t>
         </is>
       </c>
     </row>
@@ -16243,7 +16187,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>mariasolana266@movistar.es</t>
+          <t>mariasolana266@hotmail.com</t>
         </is>
       </c>
       <c r="I267" s="2" t="n">
@@ -16277,7 +16221,7 @@
       </c>
       <c r="C268" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D268" t="inlineStr">
@@ -16302,7 +16246,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>sergiomazo267@yahoo.es</t>
+          <t>sergiomazo267@hotmail.com</t>
         </is>
       </c>
       <c r="I268" s="2" t="n">
@@ -16321,11 +16265,7 @@
       <c r="L268" t="n">
         <v>0</v>
       </c>
-      <c r="M268" t="inlineStr">
-        <is>
-          <t>No hay nadie por la tarde</t>
-        </is>
-      </c>
+      <c r="M268" t="inlineStr"/>
     </row>
     <row r="269">
       <c r="A269" t="inlineStr">
@@ -16340,7 +16280,7 @@
       </c>
       <c r="C269" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D269" t="inlineStr">
@@ -16412,17 +16352,19 @@
           <t>Comillas</t>
         </is>
       </c>
-      <c r="F270" t="inlineStr">
-        <is>
-          <t>39520</t>
-        </is>
+      <c r="F270" t="n">
+        <v>39520</v>
       </c>
       <c r="G270" t="inlineStr">
         <is>
           <t>985569058</t>
         </is>
       </c>
-      <c r="H270" t="inlineStr"/>
+      <c r="H270" t="inlineStr">
+        <is>
+          <t>beatrizruiz269@hotmail.com</t>
+        </is>
+      </c>
       <c r="I270" s="2" t="n">
         <v>43123</v>
       </c>
@@ -16477,11 +16419,7 @@
           <t>+34942745544</t>
         </is>
       </c>
-      <c r="H271" t="inlineStr">
-        <is>
-          <t>lauraruiz270@yahoo.es</t>
-        </is>
-      </c>
+      <c r="H271" t="inlineStr"/>
       <c r="I271" s="2" t="n">
         <v>45171</v>
       </c>
@@ -16498,11 +16436,7 @@
       <c r="L271" t="n">
         <v>0</v>
       </c>
-      <c r="M271" t="inlineStr">
-        <is>
-          <t>Entrar por la parte de atrás</t>
-        </is>
-      </c>
+      <c r="M271" t="inlineStr"/>
     </row>
     <row r="272">
       <c r="A272" t="inlineStr">
@@ -16517,7 +16451,7 @@
       </c>
       <c r="C272" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D272" t="inlineStr">
@@ -16542,7 +16476,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>migueltrueba271@hotmail.com</t>
+          <t>migueltrueba271@yahoo.es</t>
         </is>
       </c>
       <c r="I272" s="2" t="n">
@@ -16561,7 +16495,11 @@
       <c r="L272" t="n">
         <v>0</v>
       </c>
-      <c r="M272" t="inlineStr"/>
+      <c r="M272" t="inlineStr">
+        <is>
+          <t>El reparto pasa sobre las 7 y media</t>
+        </is>
+      </c>
     </row>
     <row r="273">
       <c r="A273" t="inlineStr">
@@ -16576,7 +16514,7 @@
       </c>
       <c r="C273" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D273" t="inlineStr">
@@ -16601,7 +16539,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t>info.cafelosarcos.es</t>
+          <t>cafelosarcos272@movistar.es</t>
         </is>
       </c>
       <c r="I273" s="2" t="n">
@@ -16620,7 +16558,11 @@
       <c r="L273" t="n">
         <v>3</v>
       </c>
-      <c r="M273" t="inlineStr"/>
+      <c r="M273" t="inlineStr">
+        <is>
+          <t>Llamar antes de ir</t>
+        </is>
+      </c>
     </row>
     <row r="274">
       <c r="A274" t="inlineStr">
@@ -16660,7 +16602,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>josediego273@movistar.es</t>
+          <t>josediego273@gmail.com</t>
         </is>
       </c>
       <c r="I274" s="2" t="n">
@@ -16679,7 +16621,11 @@
       <c r="L274" t="n">
         <v>0</v>
       </c>
-      <c r="M274" t="inlineStr"/>
+      <c r="M274" t="inlineStr">
+        <is>
+          <t>Cliente antiguo</t>
+        </is>
+      </c>
     </row>
     <row r="275">
       <c r="A275" t="inlineStr">
@@ -16717,7 +16663,11 @@
           <t>+34722362826</t>
         </is>
       </c>
-      <c r="H275" t="inlineStr"/>
+      <c r="H275" t="inlineStr">
+        <is>
+          <t>sergiogutierrez274@yahoo.es</t>
+        </is>
+      </c>
       <c r="I275" s="2" t="n">
         <v>45391</v>
       </c>
@@ -16774,7 +16724,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>miguelsetien275@outlook.es</t>
+          <t>miguelsetien275@gmail.com</t>
         </is>
       </c>
       <c r="I276" s="2" t="n">
@@ -16808,7 +16758,7 @@
       </c>
       <c r="C277" t="inlineStr">
         <is>
-          <t>HOSTELERIA</t>
+          <t>hosteleria</t>
         </is>
       </c>
       <c r="D277" t="inlineStr">
@@ -16854,7 +16804,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Solo garrafas</t>
+          <t>El reparto pasa sobre las 7 y media</t>
         </is>
       </c>
     </row>
@@ -16866,7 +16816,7 @@
       </c>
       <c r="B278" t="inlineStr">
         <is>
-          <t>Bar Restaurante La Herradura S.L.</t>
+          <t>BAR RESTAURANTE LA HERRADURA S.L.</t>
         </is>
       </c>
       <c r="C278" t="inlineStr">
@@ -16876,7 +16826,7 @@
       </c>
       <c r="D278" t="inlineStr">
         <is>
-          <t>C/ Vargas, 27</t>
+          <t>C/ Vargas nº 27</t>
         </is>
       </c>
       <c r="E278" t="inlineStr">
@@ -16891,14 +16841,10 @@
       </c>
       <c r="G278" t="inlineStr">
         <is>
-          <t>651-05-38-73</t>
-        </is>
-      </c>
-      <c r="H278" t="inlineStr">
-        <is>
-          <t>barrestaurantelaherrad277@movistar.es</t>
-        </is>
-      </c>
+          <t>+34651053873</t>
+        </is>
+      </c>
+      <c r="H278" t="inlineStr"/>
       <c r="I278" s="2" t="n">
         <v>45524</v>
       </c>
@@ -16913,9 +16859,13 @@
         </is>
       </c>
       <c r="L278" t="n">
-        <v>10</v>
-      </c>
-      <c r="M278" t="inlineStr"/>
+        <v>8</v>
+      </c>
+      <c r="M278" t="inlineStr">
+        <is>
+          <t>Pide albarán siempre</t>
+        </is>
+      </c>
     </row>
     <row r="279">
       <c r="A279" t="inlineStr">
@@ -16943,8 +16893,10 @@
           <t>Santoña</t>
         </is>
       </c>
-      <c r="F279" t="n">
-        <v>39740</v>
+      <c r="F279" t="inlineStr">
+        <is>
+          <t>39740</t>
+        </is>
       </c>
       <c r="G279" t="inlineStr">
         <is>
@@ -17000,21 +16952,15 @@
           <t>Santoña</t>
         </is>
       </c>
-      <c r="F280" t="inlineStr">
-        <is>
-          <t>39740</t>
-        </is>
+      <c r="F280" t="n">
+        <v>39740</v>
       </c>
       <c r="G280" t="inlineStr">
         <is>
           <t>942 74 32 72</t>
         </is>
       </c>
-      <c r="H280" t="inlineStr">
-        <is>
-          <t>luissaiz279@hotmail.com</t>
-        </is>
-      </c>
+      <c r="H280" t="inlineStr"/>
       <c r="I280" s="2" t="n">
         <v>43120</v>
       </c>
@@ -17031,11 +16977,7 @@
       <c r="L280" t="n">
         <v>3</v>
       </c>
-      <c r="M280" t="inlineStr">
-        <is>
-          <t>Ojo con la factura</t>
-        </is>
-      </c>
+      <c r="M280" t="inlineStr"/>
     </row>
     <row r="281">
       <c r="A281" t="inlineStr">
@@ -17050,7 +16992,7 @@
       </c>
       <c r="C281" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D281" t="inlineStr">
@@ -17063,8 +17005,10 @@
           <t>Santander</t>
         </is>
       </c>
-      <c r="F281" t="n">
-        <v>39008</v>
+      <c r="F281" t="inlineStr">
+        <is>
+          <t>39008</t>
+        </is>
       </c>
       <c r="G281" t="inlineStr">
         <is>
@@ -17102,7 +17046,7 @@
       </c>
       <c r="B282" t="inlineStr">
         <is>
-          <t>CafÃ© El Faro</t>
+          <t>Café El Faro</t>
         </is>
       </c>
       <c r="C282" t="inlineStr">
@@ -17132,7 +17076,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>cafeelfaro281@gmail.com</t>
+          <t>cafeelfaro281@movistar.es</t>
         </is>
       </c>
       <c r="I282" s="2" t="n">
@@ -17161,7 +17105,7 @@
       </c>
       <c r="B283" t="inlineStr">
         <is>
-          <t>Laura LavÃ­n</t>
+          <t>Laura Lavín</t>
         </is>
       </c>
       <c r="C283" t="inlineStr">
@@ -17171,7 +17115,7 @@
       </c>
       <c r="D283" t="inlineStr">
         <is>
-          <t>C/ Santa Lucía 9</t>
+          <t>C/ Santa LucÃ­a 9</t>
         </is>
       </c>
       <c r="E283" t="inlineStr">
@@ -17189,7 +17133,11 @@
           <t>722 56 44 30</t>
         </is>
       </c>
-      <c r="H283" t="inlineStr"/>
+      <c r="H283" t="inlineStr">
+        <is>
+          <t>lauralavin282@hotmail.com</t>
+        </is>
+      </c>
       <c r="I283" s="2" t="n">
         <v>43135</v>
       </c>
@@ -17221,7 +17169,7 @@
       </c>
       <c r="C284" t="inlineStr">
         <is>
-          <t>HOSTELERIA</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D284" t="inlineStr">
@@ -17244,7 +17192,11 @@
           <t>942273151</t>
         </is>
       </c>
-      <c r="H284" t="inlineStr"/>
+      <c r="H284" t="inlineStr">
+        <is>
+          <t>cafecasaelena283@telefonica.net</t>
+        </is>
+      </c>
       <c r="I284" s="2" t="n">
         <v>45097</v>
       </c>
@@ -17276,7 +17228,7 @@
       </c>
       <c r="C285" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>hosteleria</t>
         </is>
       </c>
       <c r="D285" t="inlineStr">
@@ -17301,7 +17253,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>pensionlosarcos284@outlook.es</t>
+          <t>info@pensionlosarcos.es</t>
         </is>
       </c>
       <c r="I285" s="2" t="n">
@@ -17320,7 +17272,11 @@
       <c r="L285" t="n">
         <v>8</v>
       </c>
-      <c r="M285" t="inlineStr"/>
+      <c r="M285" t="inlineStr">
+        <is>
+          <t>Entrar por la parte de atrás</t>
+        </is>
+      </c>
     </row>
     <row r="286">
       <c r="A286" t="inlineStr">
@@ -17358,7 +17314,11 @@
           <t>985-65-86-69</t>
         </is>
       </c>
-      <c r="H286" t="inlineStr"/>
+      <c r="H286" t="inlineStr">
+        <is>
+          <t>asadoreltonel285@gmail.com</t>
+        </is>
+      </c>
       <c r="I286" s="2" t="n">
         <v>44610</v>
       </c>
@@ -17390,7 +17350,7 @@
       </c>
       <c r="C287" t="inlineStr">
         <is>
-          <t>Hostelería</t>
+          <t>hosteleria</t>
         </is>
       </c>
       <c r="D287" t="inlineStr">
@@ -17413,11 +17373,7 @@
           <t>722 94 98 24</t>
         </is>
       </c>
-      <c r="H287" t="inlineStr">
-        <is>
-          <t>info@sidreriacasajulian.es</t>
-        </is>
-      </c>
+      <c r="H287" t="inlineStr"/>
       <c r="I287" s="2" t="n">
         <v>44120</v>
       </c>
@@ -17434,7 +17390,11 @@
       <c r="L287" t="n">
         <v>10</v>
       </c>
-      <c r="M287" t="inlineStr"/>
+      <c r="M287" t="inlineStr">
+        <is>
+          <t>Entrar por la parte de atrás</t>
+        </is>
+      </c>
     </row>
     <row r="288">
       <c r="A288" t="inlineStr">
@@ -17472,11 +17432,19 @@
           <t>942-55-34-07</t>
         </is>
       </c>
-      <c r="H288" t="inlineStr"/>
+      <c r="H288" t="inlineStr">
+        <is>
+          <t>antoniorivas287@yahoo.es</t>
+        </is>
+      </c>
       <c r="I288" s="2" t="n">
         <v>42292</v>
       </c>
-      <c r="J288" t="inlineStr"/>
+      <c r="J288" t="inlineStr">
+        <is>
+          <t>RUTA-3</t>
+        </is>
+      </c>
       <c r="K288" t="inlineStr">
         <is>
           <t>domiciliado</t>
@@ -17485,7 +17453,11 @@
       <c r="L288" t="n">
         <v>0</v>
       </c>
-      <c r="M288" t="inlineStr"/>
+      <c r="M288" t="inlineStr">
+        <is>
+          <t>No hay nadie por la tarde</t>
+        </is>
+      </c>
     </row>
     <row r="289">
       <c r="A289" t="inlineStr">
@@ -17500,7 +17472,7 @@
       </c>
       <c r="C289" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D289" t="inlineStr">
@@ -17525,7 +17497,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>sarasetien288@yahoo.es</t>
+          <t>sarasetien288@telefonica.net</t>
         </is>
       </c>
       <c r="I289" s="2" t="n">
@@ -17559,7 +17531,7 @@
       </c>
       <c r="C290" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D290" t="inlineStr">
@@ -17584,7 +17556,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>elenahiguera289@hotmail.com</t>
+          <t>elenahiguera289@movistar.es</t>
         </is>
       </c>
       <c r="I290" s="2" t="n">
@@ -17603,11 +17575,7 @@
       <c r="L290" t="n">
         <v>5</v>
       </c>
-      <c r="M290" t="inlineStr">
-        <is>
-          <t>Cerrado los lunes</t>
-        </is>
-      </c>
+      <c r="M290" t="inlineStr"/>
     </row>
     <row r="291">
       <c r="A291" t="inlineStr">
@@ -17647,7 +17615,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t>nuriasalces290@telefonica.net</t>
+          <t>nuriasalces290@yahoo.es</t>
         </is>
       </c>
       <c r="I291" s="2" t="n">
@@ -17706,7 +17674,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t>pensionelpuerto291@gmail.com</t>
+          <t>pensionelpuerto291@outlook.es</t>
         </is>
       </c>
       <c r="I292" s="2" t="n">
@@ -17722,14 +17690,8 @@
           <t>domiciliado</t>
         </is>
       </c>
-      <c r="L292" t="n">
-        <v>0</v>
-      </c>
-      <c r="M292" t="inlineStr">
-        <is>
-          <t>No hay nadie por la tarde</t>
-        </is>
-      </c>
+      <c r="L292" t="inlineStr"/>
+      <c r="M292" t="inlineStr"/>
     </row>
     <row r="293">
       <c r="A293" t="inlineStr">
@@ -17744,7 +17706,7 @@
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Particular</t>
+          <t>part.</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -17769,7 +17731,7 @@
       </c>
       <c r="H293" t="inlineStr">
         <is>
-          <t>pedrofernandez292@yahoo.es</t>
+          <t>pedrofernandez292@gmail.com</t>
         </is>
       </c>
       <c r="I293" s="2" t="n">
@@ -17788,7 +17750,11 @@
       <c r="L293" t="n">
         <v>0</v>
       </c>
-      <c r="M293" t="inlineStr"/>
+      <c r="M293" t="inlineStr">
+        <is>
+          <t>Llamar antes de ir</t>
+        </is>
+      </c>
     </row>
     <row r="294">
       <c r="A294" t="inlineStr">
@@ -17828,7 +17794,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>pedrotrueba293@telefonica.net</t>
+          <t>pedrotrueba293@yahoo.es</t>
         </is>
       </c>
       <c r="I294" s="2" t="n">
@@ -17847,7 +17813,11 @@
       <c r="L294" t="n">
         <v>0</v>
       </c>
-      <c r="M294" t="inlineStr"/>
+      <c r="M294" t="inlineStr">
+        <is>
+          <t>Cliente antiguo</t>
+        </is>
+      </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
@@ -17857,17 +17827,17 @@
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>El Molino, Cafetería</t>
+          <t>CAFETERÍA EL MOLINO</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>C/ RUAMAYOR 5</t>
+          <t>Calle Ruamayor 5</t>
         </is>
       </c>
       <c r="E295" t="inlineStr">
@@ -17875,21 +17845,23 @@
           <t>Ribadesella</t>
         </is>
       </c>
-      <c r="F295" t="n">
-        <v>33560</v>
+      <c r="F295" t="inlineStr">
+        <is>
+          <t>33560</t>
+        </is>
       </c>
       <c r="G295" t="inlineStr">
         <is>
-          <t>+34722765182</t>
+          <t>722765182</t>
         </is>
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t>elmolinocafeteria294@gmail.com</t>
+          <t>cafeteriaelmolino294@outlook.es</t>
         </is>
       </c>
       <c r="I295" s="2" t="n">
-        <v>45524</v>
+        <v>45169</v>
       </c>
       <c r="J295" t="inlineStr">
         <is>
@@ -17919,7 +17891,7 @@
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -17932,19 +17904,17 @@
           <t>Santoña</t>
         </is>
       </c>
-      <c r="F296" t="n">
-        <v>39740</v>
+      <c r="F296" t="inlineStr">
+        <is>
+          <t>39740</t>
+        </is>
       </c>
       <c r="G296" t="inlineStr">
         <is>
           <t>694 45 23 63</t>
         </is>
       </c>
-      <c r="H296" t="inlineStr">
-        <is>
-          <t>restaurantelapalma295@outlook.es</t>
-        </is>
-      </c>
+      <c r="H296" t="inlineStr"/>
       <c r="I296" s="2" t="n">
         <v>43008</v>
       </c>
@@ -17971,7 +17941,7 @@
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>MARTA VILLEGAS</t>
+          <t>VILLEGAS, Marta</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
@@ -17981,7 +17951,7 @@
       </c>
       <c r="D297" t="inlineStr">
         <is>
-          <t>Calle Santa Lucía 5</t>
+          <t>C/ Santa Lucía nº 5</t>
         </is>
       </c>
       <c r="E297" t="inlineStr">
@@ -18001,11 +17971,11 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>martavillegas296@movistar.es</t>
+          <t>villegasmarta296@telefonica.net</t>
         </is>
       </c>
       <c r="I297" s="2" t="n">
-        <v>45395</v>
+        <v>43741</v>
       </c>
       <c r="J297" t="inlineStr">
         <is>
@@ -18020,7 +17990,11 @@
       <c r="L297" t="n">
         <v>0</v>
       </c>
-      <c r="M297" t="inlineStr"/>
+      <c r="M297" t="inlineStr">
+        <is>
+          <t>Cerrado los lunes</t>
+        </is>
+      </c>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
@@ -18035,12 +18009,12 @@
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
         <is>
-          <t>C/ Santa Lucía 12</t>
+          <t>C/ Santa LucÃ­a 12</t>
         </is>
       </c>
       <c r="E298" t="inlineStr">
@@ -18058,7 +18032,11 @@
           <t>942 32 57 29</t>
         </is>
       </c>
-      <c r="H298" t="inlineStr"/>
+      <c r="H298" t="inlineStr">
+        <is>
+          <t>jesusbustamante297@movistar.es</t>
+        </is>
+      </c>
       <c r="I298" s="2" t="n">
         <v>42845</v>
       </c>
@@ -18090,12 +18068,12 @@
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>part.</t>
+          <t>Particular</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
         <is>
-          <t>C/ del Río 30</t>
+          <t>C/ del RÃ­o 30</t>
         </is>
       </c>
       <c r="E299" t="inlineStr">
@@ -18115,7 +18093,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>franciscodiego298@telefonica.net</t>
+          <t>franciscodiego298@yahoo.es</t>
         </is>
       </c>
       <c r="I299" s="2" t="n">
@@ -18149,7 +18127,7 @@
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>Hostelería</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -18174,7 +18152,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>info@cerveceriaelmuelle.es</t>
+          <t>cerveceriaelmuelle299@outlook.es</t>
         </is>
       </c>
       <c r="I300" s="2" t="n">
@@ -18193,7 +18171,11 @@
       <c r="L300" t="n">
         <v>5</v>
       </c>
-      <c r="M300" t="inlineStr"/>
+      <c r="M300" t="inlineStr">
+        <is>
+          <t>Descarga complicada, calle estrecha</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -18203,17 +18185,17 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>Casa Julián, Pizzería</t>
+          <t>PIZZERÍA CASA JULIÁN SL</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>hosteleria</t>
+          <t>HOSTELERIA</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
         <is>
-          <t>C/ San Fernando, 16</t>
+          <t>C/ SAN FERNANDO 16</t>
         </is>
       </c>
       <c r="E301" t="inlineStr">
@@ -18233,11 +18215,11 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>casajulianpizzeria300@outlook.es</t>
+          <t>pizzeriacasajuliansl300@gmail.com</t>
         </is>
       </c>
       <c r="I301" s="2" t="n">
-        <v>44624</v>
+        <v>44716</v>
       </c>
       <c r="J301" t="inlineStr">
         <is>
@@ -18252,11 +18234,7 @@
       <c r="L301" t="n">
         <v>10</v>
       </c>
-      <c r="M301" t="inlineStr">
-        <is>
-          <t>Cerrado en febrero</t>
-        </is>
-      </c>
+      <c r="M301" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
